--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m13368964\Documents\Documents\1.CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-vale\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m7522667\Documents\code\acordo-judicial-reparacao-vale\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
   <si>
     <t>projeto</t>
   </si>
@@ -217,9 +217,6 @@
   </si>
   <si>
     <t>Fortalecimento da estrutura de fiscalização do Sistema Estadual de Meio Ambiente</t>
-  </si>
-  <si>
-    <t>Implantação de Fábrica de Software para construção de sistema de governança ambiental</t>
   </si>
   <si>
     <t>Ressarcimentos e contratações temporárias</t>
@@ -602,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1221,7 +1218,7 @@
         <v>49</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D44" s="1">
         <v>100000000</v>
@@ -1263,7 +1260,7 @@
         <v>52</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D47" s="1">
         <v>210000000</v>
@@ -1365,20 +1362,6 @@
       </c>
       <c r="D54" s="1">
         <v>749679</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="5">
-        <v>9288213</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" s="1">
-        <v>23000005</v>
       </c>
     </row>
   </sheetData>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
   <si>
     <t>projeto</t>
   </si>
@@ -220,6 +220,9 @@
   </si>
   <si>
     <t>Ressarcimentos e contratações temporárias</t>
+  </si>
+  <si>
+    <t>Implantação de Fábrica de Software para construção de sistema de governança ambiental</t>
   </si>
 </sst>
 </file>
@@ -599,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1364,6 +1367,20 @@
         <v>749679</v>
       </c>
     </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>9288213</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="1">
+        <v>23000005</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m7522667\Documents\code\acordo-judicial-reparacao-vale\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m13368964\Documents\Documents\1.CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-vale\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
   <si>
     <t>projeto</t>
   </si>
@@ -602,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1381,6 +1381,20 @@
         <v>23000005</v>
       </c>
     </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>9288213</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="1">
+        <v>23000005</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
   <si>
     <t xml:space="preserve">codigo_projeto</t>
   </si>
@@ -206,9 +206,6 @@
   </si>
   <si>
     <t xml:space="preserve">Fortalecimento da estrutura de fiscalização do Sistema Estadual de Meio Ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implantação de Fábrica de Software para construção de sistema de governança ambiental</t>
   </si>
 </sst>
 </file>
@@ -333,8 +330,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
-  <sheetFormatPr defaultColWidth="28.72265625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D1048576"/>
+  <sheetFormatPr defaultColWidth="28.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.57"/>
@@ -1098,48 +1095,9 @@
         <v>749679</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
-        <v>9288213</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="1" t="n">
-        <v>23000005</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
-        <v>9288213</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D56" s="1" t="n">
-        <v>23000005</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="n">
-        <v>9288213</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>23000005</v>
-      </c>
-    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.511805555555555" right="0.511805555555555" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
   <si>
     <t xml:space="preserve">codigo_projeto</t>
   </si>
@@ -331,7 +331,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="28.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="28.73828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.57"/>
@@ -1092,6 +1092,20 @@
         <v>5</v>
       </c>
       <c r="D54" s="1" t="n">
+        <v>749679</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>9288195</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="1" t="n">
         <v>749679</v>
       </c>
     </row>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
   <si>
     <t xml:space="preserve">codigo_projeto</t>
   </si>
@@ -331,7 +331,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="28.73828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="28.74609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42.57"/>
@@ -1106,6 +1106,20 @@
         <v>5</v>
       </c>
       <c r="D55" s="1" t="n">
+        <v>749679</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>9288195</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="1" t="n">
         <v>749679</v>
       </c>
     </row>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
   <si>
     <t>codigo_projeto</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>Fortalecimento da estrutura de fiscalização do Sistema Estadual de Meio Ambiente</t>
+  </si>
+  <si>
+    <t>z.Ressarcimentos e contratações temporárias</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1169,7 @@
         <v>49</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D43" s="1">
         <v>100000000</v>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m13368964\Documents\Documents\1.CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m13368964\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="63">
   <si>
     <t>codigo_projeto</t>
   </si>
@@ -212,7 +212,10 @@
     <t>Fortalecimento da estrutura de fiscalização do Sistema Estadual de Meio Ambiente</t>
   </si>
   <si>
-    <t>z.Ressarcimentos e contratações temporárias</t>
+    <t>II</t>
+  </si>
+  <si>
+    <t>Z.Ressarcimentos e contratações temporárias</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1144,7 @@
         <v>51</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D41" s="1">
         <v>99720000</v>
@@ -1169,7 +1172,7 @@
         <v>49</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D43" s="1">
         <v>100000000</v>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m13368964\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m13368964\Documents\Documents\1.CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
   <si>
     <t>codigo_projeto</t>
   </si>
@@ -212,10 +212,7 @@
     <t>Fortalecimento da estrutura de fiscalização do Sistema Estadual de Meio Ambiente</t>
   </si>
   <si>
-    <t>II</t>
-  </si>
-  <si>
-    <t>Z.Ressarcimentos e contratações temporárias</t>
+    <t>Estruturas de Apoio</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1169,7 @@
         <v>49</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D43" s="1">
         <v>100000000</v>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
   <si>
     <t>codigo_projeto</t>
   </si>
@@ -210,9 +210,6 @@
   </si>
   <si>
     <t>Fortalecimento da estrutura de fiscalização do Sistema Estadual de Meio Ambiente</t>
-  </si>
-  <si>
-    <t>Estruturas de Apoio</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1138,7 @@
         <v>51</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D41" s="1">
         <v>99720000</v>
@@ -1334,6 +1331,6 @@
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.51180555555555496" right="0.51180555555555496" top="0.78749999999999998" bottom="0.78749999999999998" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
   <si>
     <t>codigo_projeto</t>
   </si>
@@ -561,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1326,6 +1326,20 @@
         <v>800000</v>
       </c>
     </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3">
+        <v>9288214</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="1">
+        <v>800000</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A2:D56">
     <sortCondition ref="A1"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
   <si>
     <t>codigo_projeto</t>
   </si>
@@ -561,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -1340,6 +1340,20 @@
         <v>800000</v>
       </c>
     </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="3">
+        <v>9288214</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D56" s="1">
+        <v>800000</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="A2:D56">
     <sortCondition ref="A1"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -23,7 +23,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+  <si>
+    <t xml:space="preserve">codigo_projeto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">projeto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anexo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">valor_projeto</t>
+  </si>
   <si>
     <t xml:space="preserve">Melhoria da infraestrutura dos municípios</t>
   </si>
@@ -272,7 +284,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -285,16 +297,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -319,7 +327,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="28.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="28.73828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="83.71"/>
@@ -327,18 +335,18 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="28.72"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="n">
-        <v>9288130</v>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="n">
-        <v>1107550000</v>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -346,730 +354,743 @@
         <v>9288130</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>450000000</v>
+        <v>1107550000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
-        <v>9288132</v>
+        <v>9288130</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>300000000</v>
+        <v>450000000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
-        <v>9288133</v>
+        <v>9288132</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>700000000</v>
+        <v>300000000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
-        <v>9288134</v>
+        <v>9288133</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>98860000</v>
+        <v>700000000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
-        <v>9288135</v>
+        <v>9288134</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1345000</v>
+        <v>98860000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
-        <v>9288136</v>
+        <v>9288135</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>111480000</v>
+        <v>1345000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
-        <v>9288137</v>
+        <v>9288136</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>100000000</v>
+        <v>111480000</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="n">
-        <v>9288138</v>
+        <v>9288137</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>17996000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="n">
-        <v>9288139</v>
+        <v>9288138</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>3200000</v>
+        <v>14</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>17996000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
-        <v>9288141</v>
+        <v>9288139</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>500000</v>
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>3200000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="n">
-        <v>9288142</v>
+        <v>9288141</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>29712000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
-        <v>9288143</v>
+        <v>9288142</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>1</v>
+        <v>17</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>728000</v>
+        <v>29712000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="n">
-        <v>9288144</v>
+        <v>9288143</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>49000000</v>
+        <v>728000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="n">
-        <v>9288145</v>
+        <v>9288144</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>94500000</v>
+        <v>49000000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="n">
-        <v>9288147</v>
+        <v>9288145</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>14817323</v>
+        <v>94500000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="n">
-        <v>9288148</v>
+        <v>9288147</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>114995000</v>
+        <v>14817323</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="n">
-        <v>9288149</v>
+        <v>9288148</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>5000000</v>
+        <v>114995000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="n">
-        <v>9288150</v>
+        <v>9288149</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>1</v>
+        <v>23</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>10671300</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="n">
-        <v>9288152</v>
+        <v>9288150</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>1</v>
+        <v>24</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>15130000</v>
+        <v>10671300</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="n">
-        <v>9288153</v>
+        <v>9288152</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3000000</v>
+        <v>15130000</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="n">
-        <v>9288154</v>
+        <v>9288153</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>1</v>
+        <v>26</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>650000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="n">
-        <v>9288155</v>
+        <v>9288154</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>5100000</v>
+        <v>650000</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="n">
-        <v>9288167</v>
+        <v>9288155</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3773400</v>
+        <v>5100000</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="n">
-        <v>9288168</v>
+        <v>9288167</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>130000000</v>
+        <v>3773400</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="n">
-        <v>9288169</v>
+        <v>9288168</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>33248482</v>
+        <v>130000000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="n">
-        <v>9288176</v>
+        <v>9288169</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>23131467.96</v>
+        <v>31</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>33248482</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="n">
-        <v>9288177</v>
+        <v>9288176</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>100370000</v>
+        <v>32</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>23131467.96</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="n">
-        <v>9288178</v>
+        <v>9288177</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>253000000</v>
+        <v>100370000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="n">
-        <v>9288179</v>
+        <v>9288178</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>1</v>
+        <v>34</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>45000000</v>
+        <v>253000000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="n">
-        <v>9288180</v>
+        <v>9288179</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>3</v>
+        <v>35</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3072030000</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="n">
-        <v>9288181</v>
+        <v>9288180</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>552000</v>
+        <v>3072030000</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="n">
-        <v>9288182</v>
+        <v>9288181</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>1</v>
+        <v>37</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>7000000</v>
+        <v>552000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="n">
-        <v>9288183</v>
+        <v>9288182</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>1</v>
+        <v>38</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8000000</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="n">
-        <v>9288185</v>
+        <v>9288183</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D35" s="6" t="n">
-        <v>2000000</v>
+        <v>39</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>8000000</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="n">
-        <v>9288186</v>
+        <v>9288185</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>3000000</v>
+        <v>40</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>2000000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="n">
-        <v>9288187</v>
+        <v>9288186</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>1</v>
+        <v>41</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>36000000</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="n">
-        <v>9288188</v>
+        <v>9288187</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>1</v>
+        <v>42</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>8647600</v>
+        <v>36000000</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="n">
-        <v>9288189</v>
+        <v>9288188</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>1</v>
+        <v>43</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>300000</v>
+        <v>8647600</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="n">
-        <v>9288190</v>
+        <v>9288189</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>99720000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="n">
-        <v>9288191</v>
+        <v>9288190</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>210000000</v>
+        <v>99720000</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="n">
-        <v>9288192</v>
+        <v>9288191</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>100000000</v>
+        <v>210000000</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="n">
-        <v>9288193</v>
+        <v>9288192</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>1</v>
+        <v>48</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>3900000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="n">
-        <v>9288194</v>
+        <v>9288193</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>3600000</v>
+        <v>3900000</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="n">
-        <v>9288195</v>
+        <v>9288194</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>749679</v>
+        <v>3600000</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="n">
-        <v>9288196</v>
+        <v>9288195</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1800000</v>
+        <v>749679</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="n">
-        <v>9288198</v>
+        <v>9288196</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>1</v>
+        <v>52</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>985935044</v>
+        <v>1800000</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="n">
-        <v>9288209</v>
+        <v>9288198</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1200000</v>
+        <v>985935044</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="n">
-        <v>9288210</v>
+        <v>9288209</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>1</v>
+        <v>54</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>2500000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="n">
-        <v>9288211</v>
+        <v>9288210</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>1</v>
+        <v>55</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>3200000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="n">
-        <v>9288212</v>
+        <v>9288211</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>2050000000</v>
+        <v>3200000</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="n">
-        <v>9288214</v>
+        <v>9288212</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>199489167.000002</v>
+        <v>2050000000</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="n">
+        <v>9288214</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>199489167.000002</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="n">
         <v>9321270</v>
       </c>
-      <c r="B53" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D53" s="2" t="n">
+      <c r="B54" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="2" t="n">
         <v>800000</v>
       </c>
     </row>
-    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
   <si>
     <t xml:space="preserve">codigo_projeto</t>
   </si>
@@ -327,7 +327,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="28.73828125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="28.74609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="83.71"/>
@@ -1088,6 +1088,20 @@
         <v>5</v>
       </c>
       <c r="D54" s="2" t="n">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="n">
+        <v>9321270</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="2" t="n">
         <v>800000</v>
       </c>
     </row>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
   <si>
     <t xml:space="preserve">codigo_projeto</t>
   </si>
@@ -327,7 +327,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="28.74609375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="28.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="83.71"/>
@@ -1102,6 +1102,20 @@
         <v>5</v>
       </c>
       <c r="D55" s="2" t="n">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="n">
+        <v>9321270</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="2" t="n">
         <v>800000</v>
       </c>
     </row>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="61">
   <si>
     <t xml:space="preserve">codigo_projeto</t>
   </si>
@@ -327,7 +327,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="28.75" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="28.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="83.71"/>
@@ -1116,6 +1116,20 @@
         <v>5</v>
       </c>
       <c r="D56" s="2" t="n">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="n">
+        <v>9321270</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="2" t="n">
         <v>800000</v>
       </c>
     </row>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="62">
   <si>
     <t xml:space="preserve">codigo_projeto</t>
   </si>
@@ -206,6 +206,9 @@
   </si>
   <si>
     <t xml:space="preserve">Plano de Desenvolvimento da Cadeia Agropecuária</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano de Desenvolvimento da Cadeia Agropecuária1234</t>
   </si>
 </sst>
 </file>
@@ -327,7 +330,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="28.7578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="28.765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="83.71"/>
@@ -1124,7 +1127,7 @@
         <v>9321270</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>5</v>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="61">
   <si>
     <t xml:space="preserve">codigo_projeto</t>
   </si>
@@ -206,9 +206,6 @@
   </si>
   <si>
     <t xml:space="preserve">Plano de Desenvolvimento da Cadeia Agropecuária</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano de Desenvolvimento da Cadeia Agropecuária1234</t>
   </si>
 </sst>
 </file>
@@ -330,7 +327,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="28.765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="28.7734375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="83.71"/>
@@ -1127,7 +1124,7 @@
         <v>9321270</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>5</v>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C9BE0A-73EF-4AEB-AEBB-9D999849DAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="projetos" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="projetos" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">#REF!</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">#REF!</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -23,200 +28,199 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="61">
-  <si>
-    <t xml:space="preserve">codigo_projeto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">projeto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anexo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">valor_projeto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melhoria da infraestrutura dos municípios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG / conclusão de corredor logístico estruturante, conforme critérios técnicos da Seinfra / melhoria da infraestrutura dos municípios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Construção de pontes em São Francisco, Manga e São Romão sobre o Rio São Francisco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG/conclusão de corredor logístico estruturante, conforme critérios técnicos da SEINFRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realização de obras rodoviárias - Caeté - Barão de Cocais e Contorno de Barão de Cocais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implantação do Sistema de Informações Regulatórias da ARSAE-MG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reestruturação dos Hospitais da Rede FHEMIG (Hospital Infantil João Paulo II, Hospital João XXIII e Hospital Júlia Kubitschek)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ampliação da rede de rádio digital no interior do Estado de Minas Gerais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proteção policial individual e do cidadão mineiro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atualização do Plano Diretor de Desenvolvimento Integrado da Região Metropolitana de Belo Horizonte - PDDI-RMBH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Georreferenciamento de bens culturais protegidos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortalecimento da estrutura e dos processos do Instituto Mineiro de Agropecuária</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implantação da Ouvidoria 4.0 e Ouvidoria Móvel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Construção do Núcleo Integrado de Perícias da Polícia Civil de Minas Gerais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projeto ABIS - Sistema Automatizado de Identificação Biométrica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Convivência com a Seca - Construção de cisternas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortalecimento do atendimento à saúde militar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revitalização do Parque de Exposições Bolivar de Andrade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segurança Rural e de Áreas de Risco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortalecimento da competitividade turística de Minas Gerais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pesquisas, Tendências e Monitoramento da Cultura e do Turismo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano de Desenvolvimento Integrado do Turismo em Minas Gerais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortalecimento e reestruturação tecnológica da Controladoria Geral do Estado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reestruturação das Tecnologias de Informação do CBMMG</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+  <si>
+    <t>codigo_projeto</t>
+  </si>
+  <si>
+    <t>projeto</t>
+  </si>
+  <si>
+    <t>anexo</t>
+  </si>
+  <si>
+    <t>valor_projeto</t>
+  </si>
+  <si>
+    <t>Melhoria da infraestrutura dos municípios</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG / conclusão de corredor logístico estruturante, conforme critérios técnicos da Seinfra / melhoria da infraestrutura dos municípios</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>Construção de pontes em São Francisco, Manga e São Romão sobre o Rio São Francisco</t>
+  </si>
+  <si>
+    <t>Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG/conclusão de corredor logístico estruturante, conforme critérios técnicos da SEINFRA</t>
+  </si>
+  <si>
+    <t>Realização de obras rodoviárias - Caeté - Barão de Cocais e Contorno de Barão de Cocais</t>
+  </si>
+  <si>
+    <t>Implantação do Sistema de Informações Regulatórias da ARSAE-MG</t>
+  </si>
+  <si>
+    <t>Reestruturação dos Hospitais da Rede FHEMIG (Hospital Infantil João Paulo II, Hospital João XXIII e Hospital Júlia Kubitschek)</t>
+  </si>
+  <si>
+    <t>Ampliação da rede de rádio digital no interior do Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Proteção policial individual e do cidadão mineiro</t>
+  </si>
+  <si>
+    <t>Atualização do Plano Diretor de Desenvolvimento Integrado da Região Metropolitana de Belo Horizonte - PDDI-RMBH</t>
+  </si>
+  <si>
+    <t>Georreferenciamento de bens culturais protegidos</t>
+  </si>
+  <si>
+    <t>Fortalecimento da estrutura e dos processos do Instituto Mineiro de Agropecuária</t>
+  </si>
+  <si>
+    <t>Implantação da Ouvidoria 4.0 e Ouvidoria Móvel</t>
+  </si>
+  <si>
+    <t>Construção do Núcleo Integrado de Perícias da Polícia Civil de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Projeto ABIS - Sistema Automatizado de Identificação Biométrica</t>
+  </si>
+  <si>
+    <t>Convivência com a Seca - Construção de cisternas</t>
+  </si>
+  <si>
+    <t>Fortalecimento do atendimento à saúde militar</t>
+  </si>
+  <si>
+    <t>Revitalização do Parque de Exposições Bolivar de Andrade</t>
+  </si>
+  <si>
+    <t>Segurança Rural e de Áreas de Risco</t>
+  </si>
+  <si>
+    <t>Fortalecimento da competitividade turística de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Pesquisas, Tendências e Monitoramento da Cultura e do Turismo</t>
+  </si>
+  <si>
+    <t>Plano de Desenvolvimento Integrado do Turismo em Minas Gerais</t>
+  </si>
+  <si>
+    <t>Fortalecimento e reestruturação tecnológica da Controladoria Geral do Estado</t>
+  </si>
+  <si>
+    <t>Reestruturação das Tecnologias de Informação do CBMMG</t>
   </si>
   <si>
     <t xml:space="preserve">Expansão e fortalecimento da Academia do Corpo de Bombeiros Militar </t>
   </si>
   <si>
-    <t xml:space="preserve">Execução de obras e serviços de engenharia em várias unidades do CBMMG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reestruturação logística, tecnológica e de cobrança da dívida ativa da AGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melhoria da infraestrutura dos municípios - Outros repasses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prevenção de Enchentes - Construção de Bacias de Contenção no Córrego Ferrugem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prevenção de Enchentes - Desapropriação para construção de bacias de contenção no Córrego Riacho das Pedras.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reintegração social e humanização do sistema prisional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ampliação de postos de abastecimento próprios do Estado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melhoria da estrutura logística e energética da Cidade Administrativa para redução de custos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elaboração de Plano Metropolitano de Segurança Hídrica para a Região Metropolitana de Belo Horizonte.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ações de Prevenção e Combate a Incêndio em Unidades de Conservação Estaduais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consolidação das unidades de conservação no Estado de Minas Gerais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Construção e/ou manutenção de Centros de Triagem e Reabilitação de Animais Silvestres no Estado de Minas Gerais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consultoria técnica sobre a descaracterização das barragens I e II da Mundo Mineração Ltda.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estruturas de apoio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ressarcimentos de despesas públicas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ressarcimentos e contratações temporárias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contratações temporárias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implantação do Sistema de Gestão de Processos (BPMS) no Instituto Mineiro de Agropecuária (IMA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reestruturação do laboratório de química agropecuária do Instituto Mineiro de Agropecuária</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fortalecimento da estrutura de fiscalização do Sistema Estadual de Meio Ambiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estruturação operacional da Polícia Civil de Minas Gerais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conclusão de obra e Equipagem de Hospitais Regionais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estudo de viabilidade técnica e financeira e modelo de gestão da reestruturação da Fundação Ezequiel Dias – Funed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elaboração de instrumentos de gestão para desenvolvimento de mineração sustentável e competitiva - Avaliação Ambiental Estratégica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elaboração de instrumentos de gestão para desenvolvimento de mineração sustentável e competitiva - Elaboração do Plano Estadual da Mineração de Minas Gerais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estruturação, reforma e ampliação da Fundação Ezequiel Dias – Funed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plano de Desenvolvimento da Cadeia Agropecuária</t>
+    <t>Execução de obras e serviços de engenharia em várias unidades do CBMMG</t>
+  </si>
+  <si>
+    <t>Reestruturação logística, tecnológica e de cobrança da dívida ativa da AGE</t>
+  </si>
+  <si>
+    <t>Melhoria da infraestrutura dos municípios - Outros repasses</t>
+  </si>
+  <si>
+    <t>Prevenção de Enchentes - Construção de Bacias de Contenção no Córrego Ferrugem</t>
+  </si>
+  <si>
+    <t>Prevenção de Enchentes - Desapropriação para construção de bacias de contenção no Córrego Riacho das Pedras.</t>
+  </si>
+  <si>
+    <t>Implantação do Rodoanel da Região Metropolitana de Belo Horizonte</t>
+  </si>
+  <si>
+    <t>Reintegração social e humanização do sistema prisional</t>
+  </si>
+  <si>
+    <t>Ampliação de postos de abastecimento próprios do Estado</t>
+  </si>
+  <si>
+    <t>Melhoria da estrutura logística e energética da Cidade Administrativa para redução de custos</t>
+  </si>
+  <si>
+    <t>Elaboração de Plano Metropolitano de Segurança Hídrica para a Região Metropolitana de Belo Horizonte.</t>
+  </si>
+  <si>
+    <t>Ações de Prevenção e Combate a Incêndio em Unidades de Conservação Estaduais</t>
+  </si>
+  <si>
+    <t>Consolidação das unidades de conservação no Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Construção e/ou manutenção de Centros de Triagem e Reabilitação de Animais Silvestres no Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Consultoria técnica sobre a descaracterização das barragens I e II da Mundo Mineração Ltda.</t>
+  </si>
+  <si>
+    <t>Estruturas de apoio</t>
+  </si>
+  <si>
+    <t>Ressarcimentos de despesas públicas</t>
+  </si>
+  <si>
+    <t>Ressarcimentos e contratações temporárias</t>
+  </si>
+  <si>
+    <t>Contratações temporárias</t>
+  </si>
+  <si>
+    <t>Implantação do Sistema de Gestão de Processos (BPMS) no Instituto Mineiro de Agropecuária (IMA)</t>
+  </si>
+  <si>
+    <t>Reestruturação do laboratório de química agropecuária do Instituto Mineiro de Agropecuária</t>
+  </si>
+  <si>
+    <t>Fortalecimento da estrutura de fiscalização do Sistema Estadual de Meio Ambiente</t>
+  </si>
+  <si>
+    <t>Estruturação operacional da Polícia Civil de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Conclusão de obra e Equipagem de Hospitais Regionais</t>
+  </si>
+  <si>
+    <t>Estudo de viabilidade técnica e financeira e modelo de gestão da reestruturação da Fundação Ezequiel Dias – Funed</t>
+  </si>
+  <si>
+    <t>Elaboração de instrumentos de gestão para desenvolvimento de mineração sustentável e competitiva - Avaliação Ambiental Estratégica</t>
+  </si>
+  <si>
+    <t>Elaboração de instrumentos de gestão para desenvolvimento de mineração sustentável e competitiva - Elaboração do Plano Estadual da Mineração de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH</t>
+  </si>
+  <si>
+    <t>II.3</t>
+  </si>
+  <si>
+    <t>Estruturação, reforma e ampliação da Fundação Ezequiel Dias – Funed</t>
+  </si>
+  <si>
+    <t>Plano de Desenvolvimento da Cadeia Agropecuária</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -225,19 +229,11 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -249,7 +245,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -257,85 +253,350 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="28.7734375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="83.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.85"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="28.72"/>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="83.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -349,8 +610,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
         <v>9288130</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -359,12 +620,12 @@
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="2">
         <v>1107550000</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>9288130</v>
       </c>
       <c r="B3" s="4" t="s">
@@ -373,12 +634,12 @@
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="2">
         <v>450000000</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>9288132</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -387,12 +648,12 @@
       <c r="C4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="2">
         <v>300000000</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>9288133</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -401,12 +662,12 @@
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="2">
         <v>700000000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>9288134</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -415,12 +676,12 @@
       <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="2">
         <v>98860000</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>9288135</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -429,12 +690,12 @@
       <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="2">
         <v>1345000</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>9288136</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -443,12 +704,12 @@
       <c r="C8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="2">
         <v>111480000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>9288137</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -457,12 +718,12 @@
       <c r="C9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="2">
         <v>100000000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3">
         <v>9288138</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -471,12 +732,12 @@
       <c r="C10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="2">
         <v>17996000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>9288139</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -485,12 +746,12 @@
       <c r="C11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="5">
         <v>3200000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>9288141</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -499,12 +760,12 @@
       <c r="C12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="2">
         <v>500000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>9288142</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -513,12 +774,12 @@
       <c r="C13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="2">
         <v>29712000</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3">
         <v>9288143</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -527,12 +788,12 @@
       <c r="C14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="2">
         <v>728000</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
         <v>9288144</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -541,12 +802,12 @@
       <c r="C15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="2">
         <v>49000000</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3">
         <v>9288145</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -555,12 +816,12 @@
       <c r="C16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="2">
         <v>94500000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>9288147</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -569,12 +830,12 @@
       <c r="C17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="2">
         <v>14817323</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>9288148</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -583,12 +844,12 @@
       <c r="C18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="2">
         <v>114995000</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>9288149</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -597,12 +858,12 @@
       <c r="C19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="2">
         <v>5000000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>9288150</v>
       </c>
       <c r="B20" s="4" t="s">
@@ -611,12 +872,12 @@
       <c r="C20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="2" t="n">
+      <c r="D20" s="2">
         <v>10671300</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="n">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>9288152</v>
       </c>
       <c r="B21" s="4" t="s">
@@ -625,12 +886,12 @@
       <c r="C21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D21" s="2">
         <v>15130000</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="n">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3">
         <v>9288153</v>
       </c>
       <c r="B22" s="4" t="s">
@@ -639,12 +900,12 @@
       <c r="C22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="2" t="n">
+      <c r="D22" s="2">
         <v>3000000</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="n">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="3">
         <v>9288154</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -653,12 +914,12 @@
       <c r="C23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="2" t="n">
+      <c r="D23" s="2">
         <v>650000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="n">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="3">
         <v>9288155</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -667,12 +928,12 @@
       <c r="C24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D24" s="2">
         <v>5100000</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="n">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="3">
         <v>9288167</v>
       </c>
       <c r="B25" s="4" t="s">
@@ -681,12 +942,12 @@
       <c r="C25" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="2" t="n">
+      <c r="D25" s="2">
         <v>3773400</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="n">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3">
         <v>9288168</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -695,12 +956,12 @@
       <c r="C26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="2" t="n">
+      <c r="D26" s="2">
         <v>130000000</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="n">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="3">
         <v>9288169</v>
       </c>
       <c r="B27" s="4" t="s">
@@ -709,12 +970,12 @@
       <c r="C27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="2" t="n">
+      <c r="D27" s="2">
         <v>33248482</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="n">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3">
         <v>9288176</v>
       </c>
       <c r="B28" s="4" t="s">
@@ -723,12 +984,12 @@
       <c r="C28" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D28" s="5" t="n">
-        <v>23131467.96</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="n">
+      <c r="D28" s="5">
+        <v>23131467.960000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="3">
         <v>9288177</v>
       </c>
       <c r="B29" s="4" t="s">
@@ -737,12 +998,12 @@
       <c r="C29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="2" t="n">
+      <c r="D29" s="2">
         <v>100370000</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="n">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3">
         <v>9288178</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -751,12 +1012,12 @@
       <c r="C30" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D30" s="2" t="n">
+      <c r="D30" s="2">
         <v>253000000</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="n">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>9288179</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -765,12 +1026,12 @@
       <c r="C31" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="2">
         <v>45000000</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="n">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
         <v>9288180</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -779,12 +1040,12 @@
       <c r="C32" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D32" s="2" t="n">
+      <c r="D32" s="2">
         <v>3072030000</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="n">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3">
         <v>9288181</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -793,12 +1054,12 @@
       <c r="C33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D33" s="2">
         <v>552000</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="n">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3">
         <v>9288182</v>
       </c>
       <c r="B34" s="4" t="s">
@@ -807,12 +1068,12 @@
       <c r="C34" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D34" s="2" t="n">
+      <c r="D34" s="2">
         <v>7000000</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="n">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3">
         <v>9288183</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -821,12 +1082,12 @@
       <c r="C35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D35" s="2" t="n">
+      <c r="D35" s="2">
         <v>8000000</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="n">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3">
         <v>9288185</v>
       </c>
       <c r="B36" s="4" t="s">
@@ -835,12 +1096,12 @@
       <c r="C36" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D36" s="5">
         <v>2000000</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="n">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3">
         <v>9288186</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -849,12 +1110,12 @@
       <c r="C37" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D37" s="2" t="n">
+      <c r="D37" s="2">
         <v>3000000</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="n">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="3">
         <v>9288187</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -863,12 +1124,12 @@
       <c r="C38" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D38" s="2" t="n">
+      <c r="D38" s="2">
         <v>36000000</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="n">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
         <v>9288188</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -877,12 +1138,12 @@
       <c r="C39" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D39" s="2" t="n">
+      <c r="D39" s="2">
         <v>8647600</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="n">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
         <v>9288189</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -891,12 +1152,12 @@
       <c r="C40" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D40" s="2" t="n">
+      <c r="D40" s="2">
         <v>300000</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="n">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3">
         <v>9288190</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -905,12 +1166,12 @@
       <c r="C41" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D41" s="2" t="n">
+      <c r="D41" s="2">
         <v>99720000</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="n">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3">
         <v>9288191</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -919,12 +1180,12 @@
       <c r="C42" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D42" s="2" t="n">
+      <c r="D42" s="2">
         <v>210000000</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="n">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3">
         <v>9288192</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -933,12 +1194,12 @@
       <c r="C43" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="2" t="n">
+      <c r="D43" s="2">
         <v>100000000</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="3" t="n">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3">
         <v>9288193</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -947,12 +1208,12 @@
       <c r="C44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D44" s="2" t="n">
+      <c r="D44" s="2">
         <v>3900000</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="3" t="n">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3">
         <v>9288194</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -961,12 +1222,12 @@
       <c r="C45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D45" s="2">
         <v>3600000</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="3" t="n">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3">
         <v>9288195</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -975,12 +1236,12 @@
       <c r="C46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D46" s="2" t="n">
+      <c r="D46" s="2">
         <v>749679</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="n">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3">
         <v>9288196</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -989,12 +1250,12 @@
       <c r="C47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D47" s="2" t="n">
+      <c r="D47" s="2">
         <v>1800000</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="3" t="n">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3">
         <v>9288198</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -1003,12 +1264,12 @@
       <c r="C48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D48" s="2" t="n">
+      <c r="D48" s="2">
         <v>985935044</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="3" t="n">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="3">
         <v>9288209</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -1017,12 +1278,12 @@
       <c r="C49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D49" s="2" t="n">
+      <c r="D49" s="2">
         <v>1200000</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3" t="n">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="3">
         <v>9288210</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -1031,12 +1292,12 @@
       <c r="C50" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D50" s="2" t="n">
+      <c r="D50" s="2">
         <v>2500000</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="3" t="n">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3">
         <v>9288211</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -1045,12 +1306,12 @@
       <c r="C51" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D51" s="2" t="n">
+      <c r="D51" s="2">
         <v>3200000</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="3" t="n">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3">
         <v>9288212</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -1059,12 +1320,12 @@
       <c r="C52" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D52" s="2" t="n">
+      <c r="D52" s="2">
         <v>2050000000</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="3" t="n">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3">
         <v>9288214</v>
       </c>
       <c r="B53" s="4" t="s">
@@ -1073,12 +1334,12 @@
       <c r="C53" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D53" s="2" t="n">
+      <c r="D53" s="2">
         <v>199489167.000002</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="3" t="n">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="3">
         <v>9321270</v>
       </c>
       <c r="B54" s="4" t="s">
@@ -1087,62 +1348,27 @@
       <c r="C54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D54" s="2" t="n">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="3" t="n">
-        <v>9321270</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D55" s="2" t="n">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="3" t="n">
-        <v>9321270</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D56" s="2" t="n">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3" t="n">
-        <v>9321270</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D57" s="2" t="n">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="D54" s="2">
+        <v>810000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="3"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="3"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="3"/>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.511805555555555" right="0.511805555555555" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.51180555555555496" right="0.51180555555555496" top="0.78749999999999998" bottom="0.78749999999999998" header="0.51180555555555496" footer="0.51180555555555496"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\Teste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C9BE0A-73EF-4AEB-AEBB-9D999849DAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744E0528-A62A-4563-9119-6D9C7DDE2703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -591,7 +591,7 @@
   <sheetFormatPr defaultColWidth="28.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="2" max="2" width="83.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="90.5703125" style="1" customWidth="1"/>
     <col min="3" max="3" width="23.85546875" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" style="2"/>
   </cols>
@@ -1349,7 +1349,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="2">
-        <v>810000</v>
+        <v>9000000</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\Teste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744E0528-A62A-4563-9119-6D9C7DDE2703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAAEBD5-7333-4A9E-B73D-703146301E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1349,7 +1349,7 @@
         <v>5</v>
       </c>
       <c r="D54" s="2">
-        <v>9000000</v>
+        <v>8000000</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\Teste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AAAEBD5-7333-4A9E-B73D-703146301E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE48F30-5383-4F35-A985-9D528850439A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
   <si>
     <t>codigo_projeto</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>Plano de Desenvolvimento da Cadeia Agropecuária</t>
+  </si>
+  <si>
+    <t>z.Ressarcimentos e contratações temporárias</t>
   </si>
 </sst>
 </file>
@@ -592,7 +595,7 @@
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="2" width="90.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="43.85546875" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" style="2"/>
   </cols>
   <sheetData>
@@ -1178,7 +1181,7 @@
         <v>46</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D42" s="2">
         <v>210000000</v>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\Teste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE48F30-5383-4F35-A985-9D528850439A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3C2E90-E5A2-47AF-A464-441E874BEA34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
   <si>
     <t>codigo_projeto</t>
   </si>
@@ -211,9 +211,6 @@
   </si>
   <si>
     <t>Plano de Desenvolvimento da Cadeia Agropecuária</t>
-  </si>
-  <si>
-    <t>z.Ressarcimentos e contratações temporárias</t>
   </si>
 </sst>
 </file>
@@ -1181,7 +1178,7 @@
         <v>46</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D42" s="2">
         <v>210000000</v>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -26,18 +26,12 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
   <si>
-    <t>Anexo do Acordo</t>
-  </si>
-  <si>
     <t>II.3</t>
   </si>
   <si>
     <t>Elaboração de Plano Metropolitano de Segurança Hídrica para a Região Metropolitana de Belo Horizonte.</t>
   </si>
   <si>
-    <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH.</t>
-  </si>
-  <si>
     <t>III</t>
   </si>
   <si>
@@ -203,19 +197,25 @@
     <t>Melhoria da infraestrutura dos municípios</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
     <t>Melhoria da infraestrutura dos municípios - Outros repasses</t>
   </si>
   <si>
-    <t>Valor</t>
-  </si>
-  <si>
     <t>codigo_projeto</t>
   </si>
   <si>
     <t>Ressarcimentos e contratações temporárias</t>
+  </si>
+  <si>
+    <t>projeto</t>
+  </si>
+  <si>
+    <t>anexo</t>
+  </si>
+  <si>
+    <t>valor_projeto</t>
+  </si>
+  <si>
+    <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH</t>
   </si>
 </sst>
 </file>
@@ -332,7 +332,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -367,7 +367,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -555,23 +555,23 @@
   <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9.140625" style="1"/>
+    <col min="2" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -579,10 +579,10 @@
         <v>9288212</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="3">
         <v>2050000000</v>
@@ -593,10 +593,10 @@
         <v>9288130</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>450000000</v>
@@ -607,10 +607,10 @@
         <v>#N/A</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3">
         <v>427970000</v>
@@ -621,10 +621,10 @@
         <v>9288132</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3">
         <v>300000000</v>
@@ -635,10 +635,10 @@
         <v>9288180</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3">
         <v>3072030000</v>
@@ -649,10 +649,10 @@
         <v>9288133</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" s="3">
         <v>700000000</v>
@@ -663,10 +663,10 @@
         <v>9288185</v>
       </c>
       <c r="B8" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3">
         <v>2000000</v>
@@ -677,10 +677,10 @@
         <v>9288176</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" s="3">
         <f>8700000+14431467.96</f>
@@ -692,10 +692,10 @@
         <v>9288139</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3">
         <v>3200000</v>
@@ -706,10 +706,10 @@
         <v>9288135</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="3">
         <v>1345000</v>
@@ -720,10 +720,10 @@
         <v>9288169</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" s="3">
         <v>43368482</v>
@@ -734,10 +734,10 @@
         <v>9288168</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="3">
         <v>130000000</v>
@@ -748,10 +748,10 @@
         <v>9288167</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="3">
         <v>3773400</v>
@@ -762,10 +762,10 @@
         <v>9288155</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3">
         <v>5100000</v>
@@ -776,10 +776,10 @@
         <v>9288136</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3">
         <v>111480000</v>
@@ -790,10 +790,10 @@
         <v>9288214</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" s="3">
         <v>199489167.000002</v>
@@ -804,10 +804,10 @@
         <v>9288209</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D18" s="3">
         <v>1200000</v>
@@ -818,10 +818,10 @@
         <v>9288147</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="3">
         <v>14817323</v>
@@ -832,10 +832,10 @@
         <v>9288141</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>500000</v>
@@ -846,10 +846,10 @@
         <v>9288142</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" s="3">
         <v>29712000</v>
@@ -860,10 +860,10 @@
         <v>9288193</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="3">
         <v>3900000</v>
@@ -874,10 +874,10 @@
         <v>9288194</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" s="3">
         <v>3600000</v>
@@ -888,10 +888,10 @@
         <v>9288149</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D24" s="3">
         <v>5000000</v>
@@ -902,10 +902,10 @@
         <v>9288143</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="3">
         <v>728000</v>
@@ -916,10 +916,10 @@
         <v>9288144</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="3">
         <v>49000000</v>
@@ -930,10 +930,10 @@
         <v>9288196</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" s="3">
         <v>42412000</v>
@@ -944,10 +944,10 @@
         <v>9288145</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D28" s="3">
         <v>45345000</v>
@@ -958,10 +958,10 @@
         <v>9288137</v>
       </c>
       <c r="B29" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" s="3">
         <v>100000000</v>
@@ -972,10 +972,10 @@
         <v>9288148</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C30" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="3">
         <v>3000000</v>
@@ -986,10 +986,10 @@
         <v>9288138</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31" s="3">
         <v>39614000</v>
@@ -1000,10 +1000,10 @@
         <v>9288150</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C32" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32" s="3">
         <v>10671300</v>
@@ -1014,10 +1014,10 @@
         <v>9321270</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D33" s="3">
         <v>800000</v>
@@ -1028,10 +1028,10 @@
         <v>9288152</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D34" s="3">
         <v>15130000</v>
@@ -1042,10 +1042,10 @@
         <v>9288153</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D35" s="3">
         <v>3000000</v>
@@ -1056,10 +1056,10 @@
         <v>9288154</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C36" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D36" s="3">
         <v>650000</v>
@@ -1070,10 +1070,10 @@
         <v>9288210</v>
       </c>
       <c r="B37" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37" s="3">
         <v>2500000</v>
@@ -1084,10 +1084,10 @@
         <v>9288211</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C38" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38" s="3">
         <v>3200000</v>
@@ -1098,10 +1098,10 @@
         <v>9288177</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D39" s="3">
         <v>100370000</v>
@@ -1112,10 +1112,10 @@
         <v>9288177</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D40" s="3">
         <f>1048250000+59300000</f>
@@ -1127,10 +1127,10 @@
         <v>9288178</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C41" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D41" s="3">
         <v>253000000</v>
@@ -1141,10 +1141,10 @@
         <v>9288179</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C42" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D42" s="3">
         <v>45000000</v>
@@ -1155,10 +1155,10 @@
         <v>9288134</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D43" s="3">
         <v>98860000</v>
@@ -1169,10 +1169,10 @@
         <v>9288181</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C44" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D44" s="3">
         <v>75352000</v>
@@ -1183,10 +1183,10 @@
         <v>9288183</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C45" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D45" s="3">
         <v>8000000</v>
@@ -1197,10 +1197,10 @@
         <v>9288182</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D46" s="3">
         <v>7000000</v>
@@ -1211,10 +1211,10 @@
         <v>9288198</v>
       </c>
       <c r="B47" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C47" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D47" s="3">
         <v>985935044</v>
@@ -1225,10 +1225,10 @@
         <v>9288186</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D48" s="3">
         <v>3000000</v>
@@ -1239,10 +1239,10 @@
         <v>9288187</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C49" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D49" s="3">
         <v>36000000</v>
@@ -1253,10 +1253,10 @@
         <v>9288188</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D50" s="3">
         <v>8647600</v>
@@ -1267,10 +1267,10 @@
         <v>9288189</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D51" s="3">
         <v>300000</v>
@@ -1281,10 +1281,10 @@
         <v>9288195</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C52" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D52" s="3">
         <v>749679</v>
@@ -1295,10 +1295,10 @@
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D53" s="3">
         <v>23000005</v>
@@ -1309,10 +1309,10 @@
         <v>9288190</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C54" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D54" s="3">
         <v>100000000</v>
@@ -1323,10 +1323,10 @@
         <v>9288192</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C55" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D55" s="3">
         <v>100000000</v>
@@ -1337,10 +1337,10 @@
         <v>9288191</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C56" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D56" s="3">
         <v>210000000</v>
@@ -1351,10 +1351,10 @@
         <v>#N/A</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D57" s="3">
         <v>14000000</v>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -262,7 +262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -271,6 +271,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -575,723 +578,723 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>9288212</v>
+      <c r="A2" s="4">
+        <v>9288130</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3">
-        <v>2050000000</v>
+        <v>450000000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="4">
         <v>9288130</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="3">
-        <v>450000000</v>
+        <v>300000000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="e">
-        <v>#N/A</v>
+      <c r="A4" s="4">
+        <v>9288132</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <v>427970000</v>
+        <v>700000000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>9288132</v>
+      <c r="A5" s="4">
+        <v>9288133</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3">
-        <v>300000000</v>
+        <v>98860000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>9288180</v>
+      <c r="A6" s="4">
+        <v>9288134</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3">
-        <v>3072030000</v>
+        <v>1345000</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>9288133</v>
+      <c r="A7" s="4">
+        <v>9288135</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3">
-        <v>700000000</v>
+        <v>111480000</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>9288185</v>
+      <c r="A8" s="4">
+        <v>9288136</v>
       </c>
       <c r="B8" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="3">
-        <v>2000000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>9288176</v>
+      <c r="A9" s="4">
+        <v>9288137</v>
       </c>
       <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3">
+        <v>39614000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>9288138</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3200000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>9288139</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>9288141</v>
+      </c>
+      <c r="B12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="3">
+        <v>29712000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>9288142</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="3">
+        <v>728000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>9288143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="3">
+        <v>49000000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>9288144</v>
+      </c>
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="3">
+        <v>45345000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>9288145</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3">
+        <v>14817323</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>9288147</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="3">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>9288148</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>9288149</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="3">
+        <v>10671300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>9288150</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="3">
+        <v>15130000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>9288152</v>
+      </c>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="3">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>9288153</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="3">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>9288154</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="3">
+        <v>5100000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>9288155</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3773400</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>9288167</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="3">
+        <v>130000000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>9288168</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3">
+        <v>43368482</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>9288169</v>
+      </c>
+      <c r="B27" t="s">
         <v>9</v>
       </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="3">
         <f>8700000+14431467.96</f>
         <v>23131467.960000001</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9288139</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3200000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>9288135</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1345000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>9288169</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="3">
-        <v>43368482</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>9288168</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="3">
-        <v>130000000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>9288167</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="3">
-        <v>3773400</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>9288155</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="3">
-        <v>5100000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>9288136</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="3">
-        <v>111480000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>9288214</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="3">
-        <v>199489167.000002</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>9288209</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1200000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>9288147</v>
-      </c>
-      <c r="B19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="3">
-        <v>14817323</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>9288141</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="3">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>9288142</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="3">
-        <v>29712000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>9288193</v>
-      </c>
-      <c r="B22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="3">
-        <v>3900000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>9288194</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="3">
-        <v>3600000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>9288149</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="3">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>9288143</v>
-      </c>
-      <c r="B25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="3">
-        <v>728000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>9288144</v>
-      </c>
-      <c r="B26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="3">
-        <v>49000000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>9288196</v>
-      </c>
-      <c r="B27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="3">
-        <v>42412000</v>
-      </c>
-    </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>9288145</v>
+      <c r="A28" s="4">
+        <v>9288176</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="3">
-        <v>45345000</v>
+        <v>100370000</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>9288137</v>
+      <c r="A29" s="4">
+        <v>9288177</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="3">
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>9288148</v>
-      </c>
-      <c r="B30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="3">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>9288138</v>
-      </c>
-      <c r="B31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="3">
-        <v>39614000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>9288150</v>
-      </c>
-      <c r="B32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="3">
-        <v>10671300</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>9321270</v>
-      </c>
-      <c r="B33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="3">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>9288152</v>
-      </c>
-      <c r="B34" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="3">
-        <v>15130000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>9288153</v>
-      </c>
-      <c r="B35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="3">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>9288154</v>
-      </c>
-      <c r="B36" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="3">
-        <v>650000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>9288210</v>
-      </c>
-      <c r="B37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="3">
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>9288211</v>
-      </c>
-      <c r="B38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="3">
-        <v>3200000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>9288177</v>
-      </c>
-      <c r="B39" t="s">
-        <v>57</v>
-      </c>
-      <c r="C39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="3">
-        <v>100370000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>9288177</v>
-      </c>
-      <c r="B40" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="3">
         <f>1048250000+59300000</f>
         <v>1107550000</v>
       </c>
     </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>9288178</v>
+      </c>
+      <c r="B30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="3">
+        <v>253000000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>9288179</v>
+      </c>
+      <c r="B31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="3">
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>9288180</v>
+      </c>
+      <c r="B32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="3">
+        <v>3072030000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>9288181</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="3">
+        <v>75352000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>9288182</v>
+      </c>
+      <c r="B34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="3">
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>9288183</v>
+      </c>
+      <c r="B35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="3">
+        <v>8000000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>9288185</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="3">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="4">
+        <v>9288186</v>
+      </c>
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="3">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="4">
+        <v>9288187</v>
+      </c>
+      <c r="B38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="3">
+        <v>36000000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="4">
+        <v>9288188</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="3">
+        <v>8647600</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="4">
+        <v>9288189</v>
+      </c>
+      <c r="B40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="3">
+        <v>300000</v>
+      </c>
+    </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>9288178</v>
+      <c r="A41" s="4">
+        <v>9288190</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="D41" s="3">
-        <v>253000000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>9288179</v>
+      <c r="A42" s="4">
+        <v>9288191</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D42" s="3">
-        <v>45000000</v>
+        <v>210000000</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>9288134</v>
+      <c r="A43" s="4">
+        <v>9288192</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="D43" s="3">
-        <v>98860000</v>
+        <v>100000000</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>9288181</v>
+      <c r="A44" s="4">
+        <v>9288193</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="3">
-        <v>75352000</v>
+        <v>3900000</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>9288183</v>
+      <c r="A45" s="4">
+        <v>9288194</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="3">
-        <v>8000000</v>
+        <v>3600000</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>9288182</v>
+      <c r="A46" s="4">
+        <v>9288195</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="3">
-        <v>7000000</v>
+        <v>749679</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47">
+      <c r="A47" s="4">
+        <v>9288196</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="3">
+        <v>42412000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="4">
         <v>9288198</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>46</v>
       </c>
-      <c r="C47" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="3">
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="3">
         <v>985935044</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>9288186</v>
-      </c>
-      <c r="B48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C48" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="3">
-        <v>3000000</v>
-      </c>
-    </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>9288187</v>
+      <c r="A49" s="4">
+        <v>9288209</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="3">
-        <v>36000000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>9288188</v>
+      <c r="A50" s="4">
+        <v>9288210</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C50" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="3">
-        <v>8647600</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>9288189</v>
+      <c r="A51" s="4">
+        <v>9288211</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C51" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="3">
-        <v>300000</v>
+        <v>3200000</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>9288195</v>
+      <c r="A52" s="4">
+        <v>9288212</v>
       </c>
       <c r="B52" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C52" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D52" s="3">
-        <v>749679</v>
+        <v>2050000000</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53">
+      <c r="A53" s="4">
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
@@ -1305,45 +1308,45 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>9288190</v>
+      <c r="A54" s="4">
+        <v>9288214</v>
       </c>
       <c r="B54" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="D54" s="3">
-        <v>100000000</v>
+        <v>199489167.000002</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>9288192</v>
+      <c r="A55" s="4">
+        <v>9321270</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="C55" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="D55" s="3">
-        <v>100000000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>9288191</v>
+      <c r="A56" t="e">
+        <v>#N/A</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="D56" s="3">
-        <v>210000000</v>
+        <v>427970000</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -1361,6 +1364,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState ref="A2:D57">
+    <sortCondition ref="A1"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -1,23 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hugos\Desktop\Documentos Brumadinho\projeto VALE CGE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EED634-49F9-4F5F-AA34-3A8CAA58D760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6750" tabRatio="867"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="projetos" sheetId="9" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -221,7 +232,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -262,7 +273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -271,9 +282,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,7 +562,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -578,7 +586,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2">
         <v>9288130</v>
       </c>
       <c r="B2" t="s">
@@ -592,7 +600,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3">
         <v>9288130</v>
       </c>
       <c r="B3" t="s">
@@ -606,7 +614,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4">
         <v>9288132</v>
       </c>
       <c r="B4" t="s">
@@ -620,7 +628,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5">
         <v>9288133</v>
       </c>
       <c r="B5" t="s">
@@ -634,7 +642,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6">
         <v>9288134</v>
       </c>
       <c r="B6" t="s">
@@ -648,7 +656,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7">
         <v>9288135</v>
       </c>
       <c r="B7" t="s">
@@ -662,7 +670,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8">
         <v>9288136</v>
       </c>
       <c r="B8" t="s">
@@ -676,7 +684,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9">
         <v>9288137</v>
       </c>
       <c r="B9" t="s">
@@ -690,7 +698,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10">
         <v>9288138</v>
       </c>
       <c r="B10" t="s">
@@ -704,7 +712,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11">
         <v>9288139</v>
       </c>
       <c r="B11" t="s">
@@ -718,7 +726,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12">
         <v>9288141</v>
       </c>
       <c r="B12" t="s">
@@ -732,7 +740,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="A13">
         <v>9288142</v>
       </c>
       <c r="B13" t="s">
@@ -746,7 +754,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="A14">
         <v>9288143</v>
       </c>
       <c r="B14" t="s">
@@ -760,7 +768,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="A15">
         <v>9288144</v>
       </c>
       <c r="B15" t="s">
@@ -774,7 +782,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="A16">
         <v>9288145</v>
       </c>
       <c r="B16" t="s">
@@ -788,7 +796,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="A17">
         <v>9288147</v>
       </c>
       <c r="B17" t="s">
@@ -802,7 +810,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="A18">
         <v>9288148</v>
       </c>
       <c r="B18" t="s">
@@ -816,7 +824,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="A19">
         <v>9288149</v>
       </c>
       <c r="B19" t="s">
@@ -830,7 +838,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+      <c r="A20">
         <v>9288150</v>
       </c>
       <c r="B20" t="s">
@@ -844,7 +852,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+      <c r="A21">
         <v>9288152</v>
       </c>
       <c r="B21" t="s">
@@ -858,7 +866,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+      <c r="A22">
         <v>9288153</v>
       </c>
       <c r="B22" t="s">
@@ -872,7 +880,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="A23">
         <v>9288154</v>
       </c>
       <c r="B23" t="s">
@@ -886,7 +894,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="A24">
         <v>9288155</v>
       </c>
       <c r="B24" t="s">
@@ -900,7 +908,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+      <c r="A25">
         <v>9288167</v>
       </c>
       <c r="B25" t="s">
@@ -914,7 +922,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+      <c r="A26">
         <v>9288168</v>
       </c>
       <c r="B26" t="s">
@@ -928,7 +936,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+      <c r="A27">
         <v>9288169</v>
       </c>
       <c r="B27" t="s">
@@ -943,7 +951,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+      <c r="A28">
         <v>9288176</v>
       </c>
       <c r="B28" t="s">
@@ -957,7 +965,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+      <c r="A29">
         <v>9288177</v>
       </c>
       <c r="B29" t="s">
@@ -972,7 +980,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
+      <c r="A30">
         <v>9288178</v>
       </c>
       <c r="B30" t="s">
@@ -986,7 +994,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
+      <c r="A31">
         <v>9288179</v>
       </c>
       <c r="B31" t="s">
@@ -1000,7 +1008,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
+      <c r="A32">
         <v>9288180</v>
       </c>
       <c r="B32" t="s">
@@ -1014,7 +1022,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
+      <c r="A33">
         <v>9288181</v>
       </c>
       <c r="B33" t="s">
@@ -1028,7 +1036,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
+      <c r="A34">
         <v>9288182</v>
       </c>
       <c r="B34" t="s">
@@ -1042,7 +1050,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
+      <c r="A35">
         <v>9288183</v>
       </c>
       <c r="B35" t="s">
@@ -1056,7 +1064,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+      <c r="A36">
         <v>9288185</v>
       </c>
       <c r="B36" t="s">
@@ -1070,7 +1078,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
+      <c r="A37">
         <v>9288186</v>
       </c>
       <c r="B37" t="s">
@@ -1084,7 +1092,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+      <c r="A38">
         <v>9288187</v>
       </c>
       <c r="B38" t="s">
@@ -1098,7 +1106,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
+      <c r="A39">
         <v>9288188</v>
       </c>
       <c r="B39" t="s">
@@ -1112,7 +1120,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
+      <c r="A40">
         <v>9288189</v>
       </c>
       <c r="B40" t="s">
@@ -1126,7 +1134,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+      <c r="A41">
         <v>9288190</v>
       </c>
       <c r="B41" t="s">
@@ -1140,7 +1148,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+      <c r="A42">
         <v>9288191</v>
       </c>
       <c r="B42" t="s">
@@ -1154,7 +1162,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+      <c r="A43">
         <v>9288192</v>
       </c>
       <c r="B43" t="s">
@@ -1168,7 +1176,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
+      <c r="A44">
         <v>9288193</v>
       </c>
       <c r="B44" t="s">
@@ -1182,7 +1190,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+      <c r="A45">
         <v>9288194</v>
       </c>
       <c r="B45" t="s">
@@ -1196,7 +1204,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+      <c r="A46">
         <v>9288195</v>
       </c>
       <c r="B46" t="s">
@@ -1210,7 +1218,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
+      <c r="A47">
         <v>9288196</v>
       </c>
       <c r="B47" t="s">
@@ -1224,7 +1232,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4">
+      <c r="A48">
         <v>9288198</v>
       </c>
       <c r="B48" t="s">
@@ -1238,7 +1246,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
+      <c r="A49">
         <v>9288209</v>
       </c>
       <c r="B49" t="s">
@@ -1252,7 +1260,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
+      <c r="A50">
         <v>9288210</v>
       </c>
       <c r="B50" t="s">
@@ -1266,7 +1274,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
+      <c r="A51">
         <v>9288211</v>
       </c>
       <c r="B51" t="s">
@@ -1280,7 +1288,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="4">
+      <c r="A52">
         <v>9288212</v>
       </c>
       <c r="B52" t="s">
@@ -1294,7 +1302,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
+      <c r="A53">
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
@@ -1308,7 +1316,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
+      <c r="A54">
         <v>9288214</v>
       </c>
       <c r="B54" t="s">
@@ -1322,7 +1330,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="4">
+      <c r="A55">
         <v>9321270</v>
       </c>
       <c r="B55" t="s">
@@ -1364,7 +1372,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:D57">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D57">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21EED634-49F9-4F5F-AA34-3A8CAA58D760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4C0A74-34AE-4449-8073-7663AC6FB4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,7 +273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -282,6 +282,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -566,6 +567,7 @@
   <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="1"/>
@@ -586,7 +588,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="4">
         <v>9288130</v>
       </c>
       <c r="B2" t="s">
@@ -600,7 +602,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
+      <c r="A3" s="4">
         <v>9288130</v>
       </c>
       <c r="B3" t="s">
@@ -614,7 +616,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="A4" s="4">
         <v>9288132</v>
       </c>
       <c r="B4" t="s">
@@ -628,7 +630,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="4">
         <v>9288133</v>
       </c>
       <c r="B5" t="s">
@@ -642,7 +644,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="4">
         <v>9288134</v>
       </c>
       <c r="B6" t="s">
@@ -656,7 +658,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="4">
         <v>9288135</v>
       </c>
       <c r="B7" t="s">
@@ -670,7 +672,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="4">
         <v>9288136</v>
       </c>
       <c r="B8" t="s">
@@ -684,7 +686,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="4">
         <v>9288137</v>
       </c>
       <c r="B9" t="s">
@@ -698,7 +700,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="4">
         <v>9288138</v>
       </c>
       <c r="B10" t="s">
@@ -712,7 +714,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="4">
         <v>9288139</v>
       </c>
       <c r="B11" t="s">
@@ -726,7 +728,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="4">
         <v>9288141</v>
       </c>
       <c r="B12" t="s">
@@ -740,7 +742,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="4">
         <v>9288142</v>
       </c>
       <c r="B13" t="s">
@@ -754,7 +756,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="4">
         <v>9288143</v>
       </c>
       <c r="B14" t="s">
@@ -768,7 +770,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="4">
         <v>9288144</v>
       </c>
       <c r="B15" t="s">
@@ -782,7 +784,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="4">
         <v>9288145</v>
       </c>
       <c r="B16" t="s">
@@ -796,7 +798,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="4">
         <v>9288147</v>
       </c>
       <c r="B17" t="s">
@@ -810,7 +812,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="4">
         <v>9288148</v>
       </c>
       <c r="B18" t="s">
@@ -824,7 +826,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="4">
         <v>9288149</v>
       </c>
       <c r="B19" t="s">
@@ -838,7 +840,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="4">
         <v>9288150</v>
       </c>
       <c r="B20" t="s">
@@ -852,7 +854,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="4">
         <v>9288152</v>
       </c>
       <c r="B21" t="s">
@@ -866,7 +868,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="A22" s="4">
         <v>9288153</v>
       </c>
       <c r="B22" t="s">
@@ -880,7 +882,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="4">
         <v>9288154</v>
       </c>
       <c r="B23" t="s">
@@ -894,7 +896,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="A24" s="4">
         <v>9288155</v>
       </c>
       <c r="B24" t="s">
@@ -908,7 +910,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="A25" s="4">
         <v>9288167</v>
       </c>
       <c r="B25" t="s">
@@ -922,7 +924,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="A26" s="4">
         <v>9288168</v>
       </c>
       <c r="B26" t="s">
@@ -936,7 +938,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="A27" s="4">
         <v>9288169</v>
       </c>
       <c r="B27" t="s">
@@ -951,7 +953,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="A28" s="4">
         <v>9288176</v>
       </c>
       <c r="B28" t="s">
@@ -965,7 +967,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="A29" s="4">
         <v>9288177</v>
       </c>
       <c r="B29" t="s">
@@ -980,7 +982,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="A30" s="4">
         <v>9288178</v>
       </c>
       <c r="B30" t="s">
@@ -994,7 +996,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="A31" s="4">
         <v>9288179</v>
       </c>
       <c r="B31" t="s">
@@ -1008,7 +1010,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="A32" s="4">
         <v>9288180</v>
       </c>
       <c r="B32" t="s">
@@ -1022,7 +1024,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="A33" s="4">
         <v>9288181</v>
       </c>
       <c r="B33" t="s">
@@ -1036,7 +1038,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="A34" s="4">
         <v>9288182</v>
       </c>
       <c r="B34" t="s">
@@ -1050,7 +1052,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="A35" s="4">
         <v>9288183</v>
       </c>
       <c r="B35" t="s">
@@ -1064,7 +1066,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="A36" s="4">
         <v>9288185</v>
       </c>
       <c r="B36" t="s">
@@ -1078,7 +1080,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="A37" s="4">
         <v>9288186</v>
       </c>
       <c r="B37" t="s">
@@ -1092,7 +1094,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="A38" s="4">
         <v>9288187</v>
       </c>
       <c r="B38" t="s">
@@ -1106,7 +1108,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="A39" s="4">
         <v>9288188</v>
       </c>
       <c r="B39" t="s">
@@ -1120,7 +1122,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="A40" s="4">
         <v>9288189</v>
       </c>
       <c r="B40" t="s">
@@ -1134,7 +1136,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
+      <c r="A41" s="4">
         <v>9288190</v>
       </c>
       <c r="B41" t="s">
@@ -1148,7 +1150,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="A42" s="4">
         <v>9288191</v>
       </c>
       <c r="B42" t="s">
@@ -1162,7 +1164,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="A43" s="4">
         <v>9288192</v>
       </c>
       <c r="B43" t="s">
@@ -1176,7 +1178,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="A44" s="4">
         <v>9288193</v>
       </c>
       <c r="B44" t="s">
@@ -1190,7 +1192,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="A45" s="4">
         <v>9288194</v>
       </c>
       <c r="B45" t="s">
@@ -1204,7 +1206,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46">
+      <c r="A46" s="4">
         <v>9288195</v>
       </c>
       <c r="B46" t="s">
@@ -1218,7 +1220,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47">
+      <c r="A47" s="4">
         <v>9288196</v>
       </c>
       <c r="B47" t="s">
@@ -1232,7 +1234,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48">
+      <c r="A48" s="4">
         <v>9288198</v>
       </c>
       <c r="B48" t="s">
@@ -1246,7 +1248,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49">
+      <c r="A49" s="4">
         <v>9288209</v>
       </c>
       <c r="B49" t="s">
@@ -1260,7 +1262,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50">
+      <c r="A50" s="4">
         <v>9288210</v>
       </c>
       <c r="B50" t="s">
@@ -1274,7 +1276,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51">
+      <c r="A51" s="4">
         <v>9288211</v>
       </c>
       <c r="B51" t="s">
@@ -1288,7 +1290,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52">
+      <c r="A52" s="4">
         <v>9288212</v>
       </c>
       <c r="B52" t="s">
@@ -1302,7 +1304,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53">
+      <c r="A53" s="4">
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
@@ -1316,7 +1318,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54">
+      <c r="A54" s="4">
         <v>9288214</v>
       </c>
       <c r="B54" t="s">
@@ -1330,7 +1332,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55">
+      <c r="A55" s="4">
         <v>9321270</v>
       </c>
       <c r="B55" t="s">

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B4C0A74-34AE-4449-8073-7663AC6FB4AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D709A03-4578-4F6B-85D6-32EA7709D10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="projetos" sheetId="9" r:id="rId1"/>
@@ -43,6 +43,9 @@
     <t>Elaboração de Plano Metropolitano de Segurança Hídrica para a Região Metropolitana de Belo Horizonte.</t>
   </si>
   <si>
+    <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH.</t>
+  </si>
+  <si>
     <t>III</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>valor_projeto</t>
-  </si>
-  <si>
-    <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH</t>
   </si>
 </sst>
 </file>
@@ -273,7 +273,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -282,7 +282,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -344,7 +343,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -379,7 +378,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -567,734 +566,735 @@
   <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.140625" style="1"/>
+    <col min="1" max="1" width="22.5703125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="86.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2">
         <v>9288130</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
       </c>
       <c r="D2" s="3">
         <v>450000000</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>9288130</v>
+      <c r="A3">
+        <v>9288133</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3">
-        <v>300000000</v>
+        <v>700000000</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>9288132</v>
+      <c r="A4">
+        <v>9288134</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3">
-        <v>700000000</v>
+        <v>98860000</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>9288133</v>
+      <c r="A5">
+        <v>9288135</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3">
-        <v>98860000</v>
+        <v>1345000</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>9288134</v>
+      <c r="A6">
+        <v>9288136</v>
       </c>
       <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="3">
+        <v>111480000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>9288137</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="3">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>9288138</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3">
+        <v>39614000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9288139</v>
+      </c>
+      <c r="B9" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1345000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>9288135</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="3">
+        <v>3200000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9288141</v>
+      </c>
+      <c r="B10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9288142</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="3">
+        <v>29712000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>9288143</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="3">
+        <v>728000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>9288144</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="3">
+        <v>49000000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>9288145</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="3">
+        <v>45345000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>9288147</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="3">
+        <v>14817323</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>9288148</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="3">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>9288149</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="3">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>9288150</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="3">
+        <v>10671300</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>9288152</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="3">
+        <v>15130000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>9288153</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>9288154</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="3">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>9288155</v>
+      </c>
+      <c r="B22" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="3">
-        <v>111480000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>9288136</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="3">
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>9288137</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="3">
-        <v>39614000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>9288138</v>
-      </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="3">
-        <v>3200000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>9288139</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="3">
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>9288141</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="3">
-        <v>29712000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>9288142</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="3">
-        <v>728000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>9288143</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="3">
-        <v>49000000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>9288144</v>
-      </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="3">
-        <v>45345000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>9288145</v>
-      </c>
-      <c r="B16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="3">
-        <v>14817323</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>9288147</v>
-      </c>
-      <c r="B17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="3">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>9288148</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="3">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>9288149</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="3">
-        <v>10671300</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>9288150</v>
-      </c>
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="3">
-        <v>15130000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>9288152</v>
-      </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="3">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>9288153</v>
-      </c>
-      <c r="B22" t="s">
-        <v>37</v>
-      </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="3">
-        <v>650000</v>
+        <v>5100000</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
-        <v>9288154</v>
+      <c r="A23">
+        <v>9288167</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="3">
-        <v>5100000</v>
+        <v>3773400</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
-        <v>9288155</v>
+      <c r="A24">
+        <v>9288168</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="3">
-        <v>3773400</v>
+        <v>130000000</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
-        <v>9288167</v>
+      <c r="A25">
+        <v>9288169</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="3">
-        <v>130000000</v>
+        <v>43368482</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
-        <v>9288168</v>
+      <c r="A26">
+        <v>9288176</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="3">
-        <v>43368482</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
-        <v>9288169</v>
-      </c>
-      <c r="B27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="3">
         <f>8700000+14431467.96</f>
         <v>23131467.960000001</v>
       </c>
     </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>9288177</v>
+      </c>
+      <c r="B27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="3">
+        <v>100370000</v>
+      </c>
+    </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
-        <v>9288176</v>
+      <c r="A28">
+        <v>9288177</v>
       </c>
       <c r="B28" t="s">
         <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="3">
-        <v>100370000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
-        <v>9288177</v>
-      </c>
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="3">
         <f>1048250000+59300000</f>
         <v>1107550000</v>
       </c>
     </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>9288178</v>
+      </c>
+      <c r="B29" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="3">
+        <v>253000000</v>
+      </c>
+    </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
-        <v>9288178</v>
+      <c r="A30">
+        <v>9288179</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="3">
-        <v>253000000</v>
+        <v>45000000</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
-        <v>9288179</v>
+      <c r="A31">
+        <v>9288180</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D31" s="3">
-        <v>45000000</v>
+        <v>3072030000</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
-        <v>9288180</v>
+      <c r="A32">
+        <v>9288181</v>
       </c>
       <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="3">
+        <v>75352000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>9288182</v>
+      </c>
+      <c r="B33" t="s">
         <v>6</v>
       </c>
-      <c r="C32" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" s="3">
-        <v>3072030000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
-        <v>9288181</v>
-      </c>
-      <c r="B33" t="s">
-        <v>43</v>
-      </c>
       <c r="C33" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D33" s="3">
-        <v>75352000</v>
+        <v>300000000</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
+      <c r="A34">
         <v>9288182</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" s="3">
         <v>7000000</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
+      <c r="A35">
         <v>9288183</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" s="3">
         <v>8000000</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+      <c r="A36">
         <v>9288185</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" s="3">
         <v>2000000</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
+      <c r="A37">
         <v>9288186</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" s="3">
         <v>3000000</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+      <c r="A38">
         <v>9288187</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" s="3">
         <v>36000000</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
+      <c r="A39">
         <v>9288188</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="3">
         <v>8647600</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
+      <c r="A40">
         <v>9288189</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" s="3">
         <v>300000</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+      <c r="A41">
         <v>9288190</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D41" s="3">
         <v>100000000</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+      <c r="A42">
         <v>9288191</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D42" s="3">
         <v>210000000</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+      <c r="A43">
         <v>9288192</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D43" s="3">
         <v>100000000</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
+      <c r="A44">
         <v>9288193</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D44" s="3">
         <v>3900000</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+      <c r="A45">
         <v>9288194</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D45" s="3">
         <v>3600000</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+      <c r="A46">
         <v>9288195</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D46" s="3">
         <v>749679</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
+      <c r="A47">
         <v>9288196</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D47" s="3">
         <v>42412000</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4">
+      <c r="A48">
         <v>9288198</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D48" s="3">
         <v>985935044</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
+      <c r="A49">
         <v>9288209</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D49" s="3">
         <v>1200000</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
+      <c r="A50">
         <v>9288210</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D50" s="3">
         <v>2500000</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
+      <c r="A51">
         <v>9288211</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D51" s="3">
         <v>3200000</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="4">
+      <c r="A52">
         <v>9288212</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="C52" t="s">
         <v>0</v>
@@ -1304,42 +1304,42 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
+      <c r="A53">
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D53" s="3">
         <v>23000005</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
+      <c r="A54">
         <v>9288214</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D54" s="3">
         <v>199489167.000002</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="4">
+      <c r="A55">
         <v>9321270</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D55" s="3">
         <v>800000</v>
@@ -1350,10 +1350,10 @@
         <v>#N/A</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" s="3">
         <v>427970000</v>
@@ -1364,10 +1364,10 @@
         <v>#N/A</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D57" s="3">
         <v>14000000</v>
@@ -1375,7 +1375,7 @@
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D57">
-    <sortCondition ref="A1"/>
+    <sortCondition ref="A2:A57"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D709A03-4578-4F6B-85D6-32EA7709D10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19BC48AC-7097-4D8F-B26D-6944E7AD4E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="projetos" sheetId="9" r:id="rId1"/>
@@ -566,9 +566,8 @@
   <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="86.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="1"/>
+    <col min="1" max="1" width="22.5703125" customWidth="1"/>
+    <col min="2" max="2" width="86.85546875" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="9.140625" style="1"/>
   </cols>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5A569B-C724-48C1-9FB2-FF44C0224C29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90329DB9-EEFA-45C4-B1B2-7B63DBE2292D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -282,8 +282,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1350,9 +1350,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="A56" s="4"/>
       <c r="B56" t="s">
         <v>5</v>
       </c>
@@ -1364,9 +1362,7 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="e">
-        <v>#N/A</v>
-      </c>
+      <c r="A57" s="4"/>
       <c r="B57" t="s">
         <v>29</v>
       </c>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90329DB9-EEFA-45C4-B1B2-7B63DBE2292D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BF8ECE-AF48-4B8F-A2A0-E235B045284F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -282,8 +282,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
-  <workbookPr hidePivotFieldList="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andre\Documents\teletrabalho\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BF8ECE-AF48-4B8F-A2A0-E235B045284F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867"/>
   </bookViews>
   <sheets>
     <sheet name="projetos" sheetId="9" r:id="rId1"/>
@@ -232,7 +231,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -273,7 +272,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -286,6 +285,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -566,7 +566,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -592,7 +592,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+      <c r="A2" s="6">
         <v>9288130</v>
       </c>
       <c r="B2" t="s">
@@ -606,7 +606,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+      <c r="A3" s="6">
         <v>9288133</v>
       </c>
       <c r="B3" t="s">
@@ -620,7 +620,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+      <c r="A4" s="6">
         <v>9288134</v>
       </c>
       <c r="B4" t="s">
@@ -634,7 +634,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="A5" s="6">
         <v>9288135</v>
       </c>
       <c r="B5" t="s">
@@ -648,7 +648,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="A6" s="6">
         <v>9288136</v>
       </c>
       <c r="B6" t="s">
@@ -662,7 +662,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="A7" s="6">
         <v>9288137</v>
       </c>
       <c r="B7" t="s">
@@ -676,7 +676,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="A8" s="6">
         <v>9288138</v>
       </c>
       <c r="B8" t="s">
@@ -690,7 +690,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="A9" s="6">
         <v>9288139</v>
       </c>
       <c r="B9" t="s">
@@ -704,7 +704,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="A10" s="6">
         <v>9288141</v>
       </c>
       <c r="B10" t="s">
@@ -718,7 +718,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="A11" s="6">
         <v>9288142</v>
       </c>
       <c r="B11" t="s">
@@ -732,7 +732,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="A12" s="6">
         <v>9288143</v>
       </c>
       <c r="B12" t="s">
@@ -746,7 +746,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="A13" s="6">
         <v>9288144</v>
       </c>
       <c r="B13" t="s">
@@ -760,7 +760,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="A14" s="6">
         <v>9288145</v>
       </c>
       <c r="B14" t="s">
@@ -774,7 +774,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="A15" s="6">
         <v>9288147</v>
       </c>
       <c r="B15" t="s">
@@ -788,7 +788,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="A16" s="6">
         <v>9288148</v>
       </c>
       <c r="B16" t="s">
@@ -802,7 +802,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="A17" s="6">
         <v>9288149</v>
       </c>
       <c r="B17" t="s">
@@ -816,7 +816,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="A18" s="6">
         <v>9288150</v>
       </c>
       <c r="B18" t="s">
@@ -830,7 +830,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+      <c r="A19" s="6">
         <v>9288152</v>
       </c>
       <c r="B19" t="s">
@@ -844,7 +844,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+      <c r="A20" s="6">
         <v>9288153</v>
       </c>
       <c r="B20" t="s">
@@ -858,7 +858,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+      <c r="A21" s="6">
         <v>9288154</v>
       </c>
       <c r="B21" t="s">
@@ -872,7 +872,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+      <c r="A22" s="6">
         <v>9288155</v>
       </c>
       <c r="B22" t="s">
@@ -886,7 +886,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+      <c r="A23" s="6">
         <v>9288167</v>
       </c>
       <c r="B23" t="s">
@@ -900,7 +900,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+      <c r="A24" s="6">
         <v>9288168</v>
       </c>
       <c r="B24" t="s">
@@ -914,7 +914,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+      <c r="A25" s="6">
         <v>9288169</v>
       </c>
       <c r="B25" t="s">
@@ -928,7 +928,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+      <c r="A26" s="6">
         <v>9288176</v>
       </c>
       <c r="B26" t="s">
@@ -943,7 +943,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+      <c r="A27" s="6">
         <v>9288177</v>
       </c>
       <c r="B27" t="s">
@@ -957,7 +957,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+      <c r="A28" s="6">
         <v>9288177</v>
       </c>
       <c r="B28" t="s">
@@ -972,7 +972,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+      <c r="A29" s="6">
         <v>9288178</v>
       </c>
       <c r="B29" t="s">
@@ -986,7 +986,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
+      <c r="A30" s="6">
         <v>9288179</v>
       </c>
       <c r="B30" t="s">
@@ -1000,7 +1000,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
+      <c r="A31" s="6">
         <v>9288180</v>
       </c>
       <c r="B31" t="s">
@@ -1014,7 +1014,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
+      <c r="A32" s="6">
         <v>9288181</v>
       </c>
       <c r="B32" t="s">
@@ -1028,7 +1028,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
+      <c r="A33" s="6">
         <v>9288182</v>
       </c>
       <c r="B33" t="s">
@@ -1042,7 +1042,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
+      <c r="A34" s="6">
         <v>9288182</v>
       </c>
       <c r="B34" t="s">
@@ -1056,7 +1056,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
+      <c r="A35" s="6">
         <v>9288183</v>
       </c>
       <c r="B35" t="s">
@@ -1070,7 +1070,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+      <c r="A36" s="6">
         <v>9288185</v>
       </c>
       <c r="B36" t="s">
@@ -1084,7 +1084,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
+      <c r="A37" s="6">
         <v>9288186</v>
       </c>
       <c r="B37" t="s">
@@ -1098,7 +1098,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+      <c r="A38" s="6">
         <v>9288187</v>
       </c>
       <c r="B38" t="s">
@@ -1112,7 +1112,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
+      <c r="A39" s="6">
         <v>9288188</v>
       </c>
       <c r="B39" t="s">
@@ -1126,7 +1126,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
+      <c r="A40" s="6">
         <v>9288189</v>
       </c>
       <c r="B40" t="s">
@@ -1140,7 +1140,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+      <c r="A41" s="6">
         <v>9288190</v>
       </c>
       <c r="B41" t="s">
@@ -1154,7 +1154,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+      <c r="A42" s="6">
         <v>9288191</v>
       </c>
       <c r="B42" t="s">
@@ -1168,7 +1168,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+      <c r="A43" s="6">
         <v>9288192</v>
       </c>
       <c r="B43" t="s">
@@ -1182,7 +1182,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
+      <c r="A44" s="6">
         <v>9288193</v>
       </c>
       <c r="B44" t="s">
@@ -1196,7 +1196,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+      <c r="A45" s="6">
         <v>9288194</v>
       </c>
       <c r="B45" t="s">
@@ -1210,7 +1210,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+      <c r="A46" s="6">
         <v>9288195</v>
       </c>
       <c r="B46" t="s">
@@ -1224,7 +1224,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
+      <c r="A47" s="6">
         <v>9288196</v>
       </c>
       <c r="B47" t="s">
@@ -1238,7 +1238,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4">
+      <c r="A48" s="6">
         <v>9288198</v>
       </c>
       <c r="B48" t="s">
@@ -1252,7 +1252,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
+      <c r="A49" s="6">
         <v>9288209</v>
       </c>
       <c r="B49" t="s">
@@ -1266,7 +1266,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
+      <c r="A50" s="6">
         <v>9288210</v>
       </c>
       <c r="B50" t="s">
@@ -1280,7 +1280,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
+      <c r="A51" s="6">
         <v>9288211</v>
       </c>
       <c r="B51" t="s">
@@ -1294,7 +1294,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="4">
+      <c r="A52" s="6">
         <v>9288212</v>
       </c>
       <c r="B52" t="s">
@@ -1308,7 +1308,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
+      <c r="A53" s="6">
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
@@ -1322,7 +1322,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
+      <c r="A54" s="6">
         <v>9288214</v>
       </c>
       <c r="B54" t="s">
@@ -1336,7 +1336,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="4">
+      <c r="A55" s="6">
         <v>9321270</v>
       </c>
       <c r="B55" t="s">
@@ -1350,7 +1350,9 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
+      <c r="A56" s="6">
+        <v>9288214</v>
+      </c>
       <c r="B56" t="s">
         <v>5</v>
       </c>
@@ -1362,7 +1364,9 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="4"/>
+      <c r="A57" s="6">
+        <v>9321270</v>
+      </c>
       <c r="B57" t="s">
         <v>29</v>
       </c>
@@ -1374,7 +1378,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D57">
+  <sortState ref="A2:D57">
     <sortCondition ref="A2:A57"/>
   </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -5,16 +5,16 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andre\Documents\teletrabalho\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m7522667\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9600" tabRatio="867"/>
   </bookViews>
   <sheets>
     <sheet name="projetos" sheetId="9" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,9 +42,6 @@
     <t>Elaboração de Plano Metropolitano de Segurança Hídrica para a Região Metropolitana de Belo Horizonte.</t>
   </si>
   <si>
-    <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH.</t>
-  </si>
-  <si>
     <t>III</t>
   </si>
   <si>
@@ -226,6 +223,9 @@
   </si>
   <si>
     <t>valor_projeto</t>
+  </si>
+  <si>
+    <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH</t>
   </si>
 </sst>
 </file>
@@ -347,7 +347,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -382,7 +382,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -579,16 +579,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" t="s">
         <v>61</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -596,10 +596,10 @@
         <v>9288130</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3">
         <v>450000000</v>
@@ -610,10 +610,10 @@
         <v>9288133</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>700000000</v>
@@ -624,10 +624,10 @@
         <v>9288134</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3">
         <v>98860000</v>
@@ -638,10 +638,10 @@
         <v>9288135</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3">
         <v>1345000</v>
@@ -652,10 +652,10 @@
         <v>9288136</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3">
         <v>111480000</v>
@@ -666,10 +666,10 @@
         <v>9288137</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3">
         <v>100000000</v>
@@ -680,10 +680,10 @@
         <v>9288138</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3">
         <v>39614000</v>
@@ -694,10 +694,10 @@
         <v>9288139</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>3200000</v>
@@ -708,10 +708,10 @@
         <v>9288141</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3">
         <v>500000</v>
@@ -722,10 +722,10 @@
         <v>9288142</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="3">
         <v>29712000</v>
@@ -736,10 +736,10 @@
         <v>9288143</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="3">
         <v>728000</v>
@@ -750,10 +750,10 @@
         <v>9288144</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="3">
         <v>49000000</v>
@@ -764,10 +764,10 @@
         <v>9288145</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="3">
         <v>45345000</v>
@@ -778,10 +778,10 @@
         <v>9288147</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="3">
         <v>14817323</v>
@@ -792,10 +792,10 @@
         <v>9288148</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="3">
         <v>3000000</v>
@@ -806,10 +806,10 @@
         <v>9288149</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="3">
         <v>5000000</v>
@@ -820,10 +820,10 @@
         <v>9288150</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="3">
         <v>10671300</v>
@@ -834,10 +834,10 @@
         <v>9288152</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="3">
         <v>15130000</v>
@@ -848,10 +848,10 @@
         <v>9288153</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="3">
         <v>3000000</v>
@@ -862,10 +862,10 @@
         <v>9288154</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="3">
         <v>650000</v>
@@ -876,10 +876,10 @@
         <v>9288155</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="3">
         <v>5100000</v>
@@ -890,10 +890,10 @@
         <v>9288167</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="3">
         <v>3773400</v>
@@ -904,10 +904,10 @@
         <v>9288168</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="3">
         <v>130000000</v>
@@ -918,10 +918,10 @@
         <v>9288169</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="3">
         <v>43368482</v>
@@ -932,10 +932,10 @@
         <v>9288176</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="3">
         <f>8700000+14431467.96</f>
@@ -947,10 +947,10 @@
         <v>9288177</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="3">
         <v>100370000</v>
@@ -961,10 +961,10 @@
         <v>9288177</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="3">
         <f>1048250000+59300000</f>
@@ -976,10 +976,10 @@
         <v>9288178</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="3">
         <v>253000000</v>
@@ -990,10 +990,10 @@
         <v>9288179</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="3">
         <v>45000000</v>
@@ -1004,10 +1004,10 @@
         <v>9288180</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D31" s="3">
         <v>3072030000</v>
@@ -1018,10 +1018,10 @@
         <v>9288181</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="3">
         <v>75352000</v>
@@ -1032,10 +1032,10 @@
         <v>9288182</v>
       </c>
       <c r="B33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D33" s="3">
         <v>300000000</v>
@@ -1046,10 +1046,10 @@
         <v>9288182</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="3">
         <v>7000000</v>
@@ -1060,10 +1060,10 @@
         <v>9288183</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="3">
         <v>8000000</v>
@@ -1077,7 +1077,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="3">
         <v>2000000</v>
@@ -1088,10 +1088,10 @@
         <v>9288186</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="3">
         <v>3000000</v>
@@ -1102,10 +1102,10 @@
         <v>9288187</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="3">
         <v>36000000</v>
@@ -1116,10 +1116,10 @@
         <v>9288188</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="3">
         <v>8647600</v>
@@ -1130,10 +1130,10 @@
         <v>9288189</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="3">
         <v>300000</v>
@@ -1144,10 +1144,10 @@
         <v>9288190</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D41" s="3">
         <v>100000000</v>
@@ -1158,10 +1158,10 @@
         <v>9288191</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D42" s="3">
         <v>210000000</v>
@@ -1172,10 +1172,10 @@
         <v>9288192</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C43" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D43" s="3">
         <v>100000000</v>
@@ -1186,10 +1186,10 @@
         <v>9288193</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D44" s="3">
         <v>3900000</v>
@@ -1200,10 +1200,10 @@
         <v>9288194</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" s="3">
         <v>3600000</v>
@@ -1214,10 +1214,10 @@
         <v>9288195</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D46" s="3">
         <v>749679</v>
@@ -1228,10 +1228,10 @@
         <v>9288196</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47" s="3">
         <v>42412000</v>
@@ -1242,10 +1242,10 @@
         <v>9288198</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D48" s="3">
         <v>985935044</v>
@@ -1256,10 +1256,10 @@
         <v>9288209</v>
       </c>
       <c r="B49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D49" s="3">
         <v>1200000</v>
@@ -1270,10 +1270,10 @@
         <v>9288210</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D50" s="3">
         <v>2500000</v>
@@ -1284,10 +1284,10 @@
         <v>9288211</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51" s="3">
         <v>3200000</v>
@@ -1298,7 +1298,7 @@
         <v>9288212</v>
       </c>
       <c r="B52" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="C52" t="s">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" s="3">
         <v>23000005</v>
@@ -1326,10 +1326,10 @@
         <v>9288214</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54" s="3">
         <v>199489167.000002</v>
@@ -1340,10 +1340,10 @@
         <v>9321270</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55" s="3">
         <v>800000</v>
@@ -1354,10 +1354,10 @@
         <v>9288214</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" s="3">
         <v>427970000</v>
@@ -1368,10 +1368,10 @@
         <v>9321270</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D57" s="3">
         <v>14000000</v>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -42,6 +42,9 @@
     <t>Elaboração de Plano Metropolitano de Segurança Hídrica para a Região Metropolitana de Belo Horizonte.</t>
   </si>
   <si>
+    <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH.</t>
+  </si>
+  <si>
     <t>III</t>
   </si>
   <si>
@@ -223,9 +226,6 @@
   </si>
   <si>
     <t>valor_projeto</t>
-  </si>
-  <si>
-    <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH</t>
   </si>
 </sst>
 </file>
@@ -579,16 +579,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -596,10 +596,10 @@
         <v>9288130</v>
       </c>
       <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>2</v>
       </c>
       <c r="D2" s="3">
         <v>450000000</v>
@@ -610,10 +610,10 @@
         <v>9288133</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3">
         <v>700000000</v>
@@ -624,10 +624,10 @@
         <v>9288134</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3">
         <v>98860000</v>
@@ -638,10 +638,10 @@
         <v>9288135</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3">
         <v>1345000</v>
@@ -652,10 +652,10 @@
         <v>9288136</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3">
         <v>111480000</v>
@@ -666,10 +666,10 @@
         <v>9288137</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="3">
         <v>100000000</v>
@@ -680,10 +680,10 @@
         <v>9288138</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="3">
         <v>39614000</v>
@@ -694,10 +694,10 @@
         <v>9288139</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="3">
         <v>3200000</v>
@@ -708,10 +708,10 @@
         <v>9288141</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3">
         <v>500000</v>
@@ -722,10 +722,10 @@
         <v>9288142</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="3">
         <v>29712000</v>
@@ -736,10 +736,10 @@
         <v>9288143</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="3">
         <v>728000</v>
@@ -750,10 +750,10 @@
         <v>9288144</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="3">
         <v>49000000</v>
@@ -764,10 +764,10 @@
         <v>9288145</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="3">
         <v>45345000</v>
@@ -778,10 +778,10 @@
         <v>9288147</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="3">
         <v>14817323</v>
@@ -792,10 +792,10 @@
         <v>9288148</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3">
         <v>3000000</v>
@@ -806,10 +806,10 @@
         <v>9288149</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="3">
         <v>5000000</v>
@@ -820,10 +820,10 @@
         <v>9288150</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="3">
         <v>10671300</v>
@@ -834,10 +834,10 @@
         <v>9288152</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="3">
         <v>15130000</v>
@@ -848,10 +848,10 @@
         <v>9288153</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="3">
         <v>3000000</v>
@@ -862,10 +862,10 @@
         <v>9288154</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="3">
         <v>650000</v>
@@ -876,10 +876,10 @@
         <v>9288155</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="3">
         <v>5100000</v>
@@ -890,10 +890,10 @@
         <v>9288167</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="3">
         <v>3773400</v>
@@ -904,10 +904,10 @@
         <v>9288168</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="3">
         <v>130000000</v>
@@ -918,10 +918,10 @@
         <v>9288169</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="3">
         <v>43368482</v>
@@ -932,10 +932,10 @@
         <v>9288176</v>
       </c>
       <c r="B26" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="3">
         <f>8700000+14431467.96</f>
@@ -947,10 +947,10 @@
         <v>9288177</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="3">
         <v>100370000</v>
@@ -961,10 +961,10 @@
         <v>9288177</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="3">
         <f>1048250000+59300000</f>
@@ -976,10 +976,10 @@
         <v>9288178</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="3">
         <v>253000000</v>
@@ -990,10 +990,10 @@
         <v>9288179</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="3">
         <v>45000000</v>
@@ -1004,10 +1004,10 @@
         <v>9288180</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C31" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" s="3">
         <v>3072030000</v>
@@ -1018,10 +1018,10 @@
         <v>9288181</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="3">
         <v>75352000</v>
@@ -1032,10 +1032,10 @@
         <v>9288182</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D33" s="3">
         <v>300000000</v>
@@ -1046,10 +1046,10 @@
         <v>9288182</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34" s="3">
         <v>7000000</v>
@@ -1060,10 +1060,10 @@
         <v>9288183</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D35" s="3">
         <v>8000000</v>
@@ -1077,7 +1077,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" s="3">
         <v>2000000</v>
@@ -1088,10 +1088,10 @@
         <v>9288186</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" s="3">
         <v>3000000</v>
@@ -1102,10 +1102,10 @@
         <v>9288187</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" s="3">
         <v>36000000</v>
@@ -1116,10 +1116,10 @@
         <v>9288188</v>
       </c>
       <c r="B39" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="3">
         <v>8647600</v>
@@ -1130,10 +1130,10 @@
         <v>9288189</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" s="3">
         <v>300000</v>
@@ -1144,10 +1144,10 @@
         <v>9288190</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D41" s="3">
         <v>100000000</v>
@@ -1158,10 +1158,10 @@
         <v>9288191</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C42" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D42" s="3">
         <v>210000000</v>
@@ -1172,10 +1172,10 @@
         <v>9288192</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D43" s="3">
         <v>100000000</v>
@@ -1186,10 +1186,10 @@
         <v>9288193</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D44" s="3">
         <v>3900000</v>
@@ -1200,10 +1200,10 @@
         <v>9288194</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D45" s="3">
         <v>3600000</v>
@@ -1214,10 +1214,10 @@
         <v>9288195</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D46" s="3">
         <v>749679</v>
@@ -1228,10 +1228,10 @@
         <v>9288196</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C47" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D47" s="3">
         <v>42412000</v>
@@ -1242,10 +1242,10 @@
         <v>9288198</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D48" s="3">
         <v>985935044</v>
@@ -1256,10 +1256,10 @@
         <v>9288209</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D49" s="3">
         <v>1200000</v>
@@ -1270,10 +1270,10 @@
         <v>9288210</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D50" s="3">
         <v>2500000</v>
@@ -1284,10 +1284,10 @@
         <v>9288211</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D51" s="3">
         <v>3200000</v>
@@ -1298,7 +1298,7 @@
         <v>9288212</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="C52" t="s">
         <v>0</v>
@@ -1312,10 +1312,10 @@
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D53" s="3">
         <v>23000005</v>
@@ -1326,10 +1326,10 @@
         <v>9288214</v>
       </c>
       <c r="B54" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C54" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D54" s="3">
         <v>199489167.000002</v>
@@ -1340,10 +1340,10 @@
         <v>9321270</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C55" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D55" s="3">
         <v>800000</v>
@@ -1354,10 +1354,10 @@
         <v>9288214</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C56" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" s="3">
         <v>427970000</v>
@@ -1368,10 +1368,10 @@
         <v>9321270</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D57" s="3">
         <v>14000000</v>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -1,40 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m7522667\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <workbookPr hidePivotFieldList="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="9600" tabRatio="867"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320" tabRatio="867"/>
   </bookViews>
   <sheets>
     <sheet name="projetos" sheetId="9" r:id="rId1"/>
+    <sheet name="Plan1" sheetId="10" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">projetos!$A$1:$D$56</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
   <si>
     <t>II.3</t>
   </si>
@@ -42,18 +31,12 @@
     <t>Elaboração de Plano Metropolitano de Segurança Hídrica para a Região Metropolitana de Belo Horizonte.</t>
   </si>
   <si>
-    <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH.</t>
-  </si>
-  <si>
     <t>III</t>
   </si>
   <si>
     <t>Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG / conclusão de corredor logístico estruturante, conforme critérios técnicos da Seinfra / melhoria da infraestrutura dos municípios</t>
   </si>
   <si>
-    <t>Complementação dos recursos federais para o Metrô da RMBH</t>
-  </si>
-  <si>
     <t>Construção de pontes em São Francisco, Manga e São Romão sobre o Rio São Francisco</t>
   </si>
   <si>
@@ -226,16 +209,19 @@
   </si>
   <si>
     <t>valor_projeto</t>
+  </si>
+  <si>
+    <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,7 +258,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -281,15 +267,16 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
+    <cellStyle name="Separador de milhares" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -347,7 +334,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -382,7 +369,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -559,746 +546,748 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D57"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D56"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="86.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="29" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
         <v>9288130</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3">
         <v>450000000</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>9288130</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3">
+        <f>1048250000+59300000</f>
+        <v>1107550000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>9288132</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>300000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
         <v>9288133</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3">
         <v>700000000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+    <row r="6" spans="1:4">
+      <c r="A6">
         <v>9288134</v>
       </c>
-      <c r="B4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3">
+        <v>98860000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>9288135</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1345000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>9288136</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3">
+        <v>111480000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>9288137</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>9288138</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3">
+        <v>39614000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>9288139</v>
+      </c>
+      <c r="B11" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3">
-        <v>98860000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
-        <v>9288135</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1345000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>9288136</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="3">
-        <v>111480000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
-        <v>9288137</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3">
-        <v>100000000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
-        <v>9288138</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="3">
-        <v>39614000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
-        <v>9288139</v>
-      </c>
-      <c r="B9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="3">
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3">
         <v>3200000</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+    <row r="12" spans="1:4">
+      <c r="A12">
         <v>9288141</v>
       </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="3">
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3">
         <v>500000</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+    <row r="13" spans="1:4">
+      <c r="A13">
         <v>9288142</v>
       </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3">
         <v>29712000</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+    <row r="14" spans="1:4">
+      <c r="A14">
         <v>9288143</v>
       </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="3">
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3">
         <v>728000</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+    <row r="15" spans="1:4">
+      <c r="A15">
         <v>9288144</v>
       </c>
-      <c r="B13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="3">
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3">
         <v>49000000</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+    <row r="16" spans="1:4">
+      <c r="A16">
         <v>9288145</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3">
+        <v>45345000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>9288147</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3">
+        <v>14817323</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>9288148</v>
+      </c>
+      <c r="B18" t="s">
         <v>30</v>
       </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="3">
-        <v>45345000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
-        <v>9288147</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="3">
-        <v>14817323</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
-        <v>9288148</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="3">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>9288149</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3">
+        <v>5000000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>9288150</v>
+      </c>
+      <c r="B20" t="s">
         <v>32</v>
       </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3">
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="3">
+        <v>10671300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>9288152</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3">
+        <v>15130000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>9288153</v>
+      </c>
+      <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3">
         <v>3000000</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>9288149</v>
-      </c>
-      <c r="B17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="3">
-        <v>5000000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
-        <v>9288150</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="3">
-        <v>10671300</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
-        <v>9288152</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>9288154</v>
+      </c>
+      <c r="B23" t="s">
         <v>36</v>
       </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="3">
-        <v>15130000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
-        <v>9288153</v>
-      </c>
-      <c r="B20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="3">
-        <v>3000000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
-        <v>9288154</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
         <v>650000</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+    <row r="24" spans="1:4">
+      <c r="A24">
         <v>9288155</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="3">
-        <v>5100000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>9288167</v>
-      </c>
-      <c r="B23" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="3">
-        <v>3773400</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
-        <v>9288168</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" s="3">
-        <v>130000000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
-        <v>9288169</v>
+        <v>5100000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
+        <v>9288167</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" s="3">
+        <v>3773400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
+        <v>9288168</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3">
+        <v>130000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>9288169</v>
+      </c>
+      <c r="B27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="3">
         <v>43368482</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+    <row r="28" spans="1:4">
+      <c r="A28">
         <v>9288176</v>
       </c>
-      <c r="B26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="3">
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3">
         <f>8700000+14431467.96</f>
         <v>23131467.960000001</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+    <row r="29" spans="1:4">
+      <c r="A29">
         <v>9288177</v>
       </c>
-      <c r="B27" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="3">
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3">
         <v>100370000</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
-        <v>9288177</v>
-      </c>
-      <c r="B28" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="3">
-        <f>1048250000+59300000</f>
-        <v>1107550000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+    <row r="30" spans="1:4">
+      <c r="A30">
         <v>9288178</v>
       </c>
-      <c r="B29" t="s">
-        <v>41</v>
-      </c>
-      <c r="C29" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="3">
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3">
         <v>253000000</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+    <row r="31" spans="1:4">
+      <c r="A31">
         <v>9288179</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3">
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32">
+        <v>9288180</v>
+      </c>
+      <c r="B32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="3">
+        <v>3072030000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33">
+        <v>9288181</v>
+      </c>
+      <c r="B33" t="s">
         <v>42</v>
       </c>
-      <c r="C30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="3">
-        <v>45000000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
-        <v>9288180</v>
-      </c>
-      <c r="B31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="3">
-        <v>3072030000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
-        <v>9288181</v>
-      </c>
-      <c r="B32" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="3">
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="3">
         <v>75352000</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+    <row r="34" spans="1:4">
+      <c r="A34">
         <v>9288182</v>
       </c>
-      <c r="B33" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="3">
-        <v>300000000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
-        <v>9288182</v>
-      </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D34" s="3">
         <v>7000000</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+    <row r="35" spans="1:4">
+      <c r="A35">
         <v>9288183</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D35" s="3">
         <v>8000000</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+    <row r="36" spans="1:4">
+      <c r="A36">
         <v>9288185</v>
       </c>
       <c r="B36" t="s">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D36" s="3">
         <v>2000000</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
+    <row r="37" spans="1:4">
+      <c r="A37">
         <v>9288186</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D37" s="3">
         <v>3000000</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+    <row r="38" spans="1:4">
+      <c r="A38">
         <v>9288187</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D38" s="3">
         <v>36000000</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+    <row r="39" spans="1:4">
+      <c r="A39">
         <v>9288188</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C39" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D39" s="3">
         <v>8647600</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+    <row r="40" spans="1:4">
+      <c r="A40">
         <v>9288189</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C40" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D40" s="3">
         <v>300000</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
+    <row r="41" spans="1:4">
+      <c r="A41">
         <v>9288190</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D41" s="3">
         <v>100000000</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
+    <row r="42" spans="1:4">
+      <c r="A42">
         <v>9288191</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D42" s="3">
         <v>210000000</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
+    <row r="43" spans="1:4">
+      <c r="A43">
         <v>9288192</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D43" s="3">
         <v>100000000</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
+    <row r="44" spans="1:4">
+      <c r="A44">
         <v>9288193</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D44" s="3">
         <v>3900000</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
+    <row r="45" spans="1:4">
+      <c r="A45">
         <v>9288194</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D45" s="3">
         <v>3600000</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+    <row r="46" spans="1:4">
+      <c r="A46">
         <v>9288195</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D46" s="3">
         <v>749679</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
+    <row r="47" spans="1:4">
+      <c r="A47">
         <v>9288196</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D47" s="3">
         <v>42412000</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
+    <row r="48" spans="1:4">
+      <c r="A48">
         <v>9288198</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C48" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D48" s="3">
         <v>985935044</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
+    <row r="49" spans="1:4">
+      <c r="A49">
         <v>9288209</v>
       </c>
       <c r="B49" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D49" s="3">
         <v>1200000</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
+    <row r="50" spans="1:4">
+      <c r="A50">
         <v>9288210</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C50" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D50" s="3">
         <v>2500000</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
+    <row r="51" spans="1:4">
+      <c r="A51">
         <v>9288211</v>
       </c>
       <c r="B51" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D51" s="3">
         <v>3200000</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+    <row r="52" spans="1:4">
+      <c r="A52">
         <v>9288212</v>
       </c>
       <c r="B52" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s">
         <v>0</v>
@@ -1307,81 +1296,78 @@
         <v>2050000000</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+    <row r="53" spans="1:4">
+      <c r="A53">
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D53" s="3">
         <v>23000005</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+    <row r="54" spans="1:4">
+      <c r="A54">
         <v>9288214</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="3">
         <v>199489167.000002</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+    <row r="55" spans="1:4">
+      <c r="A55">
         <v>9321270</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C55" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D55" s="3">
         <v>800000</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
-        <v>9288214</v>
+    <row r="56" spans="1:4">
+      <c r="A56">
+        <v>9334530</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D56" s="3">
-        <v>427970000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>9321270</v>
-      </c>
-      <c r="B57" t="s">
-        <v>29</v>
-      </c>
-      <c r="C57" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="3">
         <v>14000000</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:D57">
-    <sortCondition ref="A2:A57"/>
-  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
   <si>
     <t>II.3</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>Intervenções e Obras a serem realizadas, sob a responsabilidade e de propriedade do Estado de Minas Gerais, com o objetivo de aumentar a resiliência das Bacias do Paraopeba e Rio das Velhas, de modo a garantir o abastecimento da Região Metropolitana de Belo Horizonte - RMBH</t>
+  </si>
+  <si>
+    <t>Complementação dos recursos federais para o Metrô da RMBH</t>
   </si>
 </sst>
 </file>
@@ -258,7 +261,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -273,6 +276,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -546,7 +550,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -554,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1350,6 +1354,20 @@
       </c>
       <c r="D56" s="3">
         <v>14000000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="1">
+        <v>9999999</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" s="2">
+        <v>427970000</v>
       </c>
     </row>
   </sheetData>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
   <workbookPr hidePivotFieldList="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320" tabRatio="867"/>
@@ -13,9 +13,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">projetos!$A$1:$D$56</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="144525"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -61,9 +61,6 @@
     <t>Execução de obras e serviços de engenharia em várias unidades do CBMMG</t>
   </si>
   <si>
-    <t xml:space="preserve">Expansão e fortalecimento da Academia do Corpo de Bombeiros Militar </t>
-  </si>
-  <si>
     <t>Reestruturação das Tecnologias de Informação do CBMMG</t>
   </si>
   <si>
@@ -215,16 +212,19 @@
   </si>
   <si>
     <t>Complementação dos recursos federais para o Metrô da RMBH</t>
+  </si>
+  <si>
+    <t>Expansão e fortalecimento da Academia do Corpo de Bombeiros Militar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,7 +280,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Separador de milhares" xfId="1" builtinId="3"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -550,16 +550,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="29" style="1" customWidth="1"/>
@@ -570,21 +570,21 @@
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9288130</v>
       </c>
@@ -598,22 +598,21 @@
         <v>450000000</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9288130</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3">
-        <f>1048250000+59300000</f>
         <v>1107550000</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9288132</v>
       </c>
@@ -627,7 +626,7 @@
         <v>300000000</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9288133</v>
       </c>
@@ -641,12 +640,12 @@
         <v>700000000</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9288134</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -655,7 +654,7 @@
         <v>98860000</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9288135</v>
       </c>
@@ -669,12 +668,12 @@
         <v>1345000</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9288136</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
@@ -683,12 +682,12 @@
         <v>111480000</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9288137</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
@@ -697,12 +696,12 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9288138</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
@@ -711,7 +710,7 @@
         <v>39614000</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9288139</v>
       </c>
@@ -725,12 +724,12 @@
         <v>3200000</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9288141</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
@@ -739,12 +738,12 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9288142</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
@@ -753,12 +752,12 @@
         <v>29712000</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9288143</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
         <v>7</v>
@@ -767,12 +766,12 @@
         <v>728000</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9288144</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
@@ -781,12 +780,12 @@
         <v>49000000</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9288145</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
@@ -795,12 +794,12 @@
         <v>45345000</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9288147</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
         <v>7</v>
@@ -809,12 +808,12 @@
         <v>14817323</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9288148</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
@@ -823,12 +822,12 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9288149</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
@@ -837,12 +836,12 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9288150</v>
       </c>
       <c r="B20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
@@ -851,12 +850,12 @@
         <v>10671300</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9288152</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -865,12 +864,12 @@
         <v>15130000</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9288153</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
         <v>7</v>
@@ -879,12 +878,12 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9288154</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
         <v>7</v>
@@ -893,12 +892,12 @@
         <v>650000</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9288155</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
@@ -907,12 +906,12 @@
         <v>5100000</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9288167</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
@@ -921,12 +920,12 @@
         <v>3773400</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9288168</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
@@ -935,7 +934,7 @@
         <v>130000000</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9288169</v>
       </c>
@@ -949,7 +948,7 @@
         <v>43368482</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9288176</v>
       </c>
@@ -960,16 +959,15 @@
         <v>7</v>
       </c>
       <c r="D28" s="3">
-        <f>8700000+14431467.96</f>
         <v>23131467.960000001</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9288177</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
         <v>7</v>
@@ -978,12 +976,12 @@
         <v>100370000</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9288178</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
@@ -992,12 +990,12 @@
         <v>253000000</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9288179</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
         <v>7</v>
@@ -1006,7 +1004,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9288180</v>
       </c>
@@ -1020,12 +1018,12 @@
         <v>3072030000</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9288181</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
@@ -1034,12 +1032,12 @@
         <v>75352000</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9288182</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
         <v>7</v>
@@ -1048,12 +1046,12 @@
         <v>7000000</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9288183</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
         <v>7</v>
@@ -1062,7 +1060,7 @@
         <v>8000000</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9288185</v>
       </c>
@@ -1076,12 +1074,12 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9288186</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" t="s">
         <v>7</v>
@@ -1090,12 +1088,12 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>9288187</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
         <v>7</v>
@@ -1104,12 +1102,12 @@
         <v>36000000</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>9288188</v>
       </c>
       <c r="B39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C39" t="s">
         <v>7</v>
@@ -1118,12 +1116,12 @@
         <v>8647600</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>9288189</v>
       </c>
       <c r="B40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40" t="s">
         <v>7</v>
@@ -1132,54 +1130,54 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>9288190</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D41" s="3">
         <v>100000000</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>9288191</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D42" s="3">
         <v>210000000</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>9288192</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D43" s="3">
         <v>100000000</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>9288193</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C44" t="s">
         <v>7</v>
@@ -1188,12 +1186,12 @@
         <v>3900000</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>9288194</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C45" t="s">
         <v>7</v>
@@ -1202,12 +1200,12 @@
         <v>3600000</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9288195</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
         <v>7</v>
@@ -1216,12 +1214,12 @@
         <v>749679</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>9288196</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
         <v>7</v>
@@ -1230,12 +1228,12 @@
         <v>42412000</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>9288198</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" t="s">
         <v>7</v>
@@ -1244,12 +1242,12 @@
         <v>985935044</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>9288209</v>
       </c>
       <c r="B49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C49" t="s">
         <v>7</v>
@@ -1258,12 +1256,12 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>9288210</v>
       </c>
       <c r="B50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C50" t="s">
         <v>7</v>
@@ -1272,12 +1270,12 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>9288211</v>
       </c>
       <c r="B51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C51" t="s">
         <v>7</v>
@@ -1286,12 +1284,12 @@
         <v>3200000</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>9288212</v>
       </c>
       <c r="B52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
         <v>0</v>
@@ -1300,12 +1298,12 @@
         <v>2050000000</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C53" t="s">
         <v>7</v>
@@ -1314,12 +1312,12 @@
         <v>23000005</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>9288214</v>
       </c>
       <c r="B54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C54" t="s">
         <v>7</v>
@@ -1328,12 +1326,12 @@
         <v>199489167.000002</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>9321270</v>
       </c>
       <c r="B55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C55" t="s">
         <v>7</v>
@@ -1342,12 +1340,12 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>9334530</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C56" t="s">
         <v>7</v>
@@ -1356,12 +1354,12 @@
         <v>14000000</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>9999999</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>2</v>
@@ -1377,9 +1375,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="6.7109375" bestFit="1" customWidth="1"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
   <workbookPr hidePivotFieldList="1"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6299D06-EE63-429C-BEF3-4B744F9C17CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7320" tabRatio="867"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="projetos" sheetId="9" r:id="rId1"/>
@@ -13,10 +19,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">projetos!$A$1:$D$56</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -220,11 +236,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,7 +296,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Separador de milhares" xfId="1" builtinId="3"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -550,16 +566,16 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="29" style="1" customWidth="1"/>
@@ -570,7 +586,7 @@
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>57</v>
       </c>
@@ -584,7 +600,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9288130</v>
       </c>
@@ -598,7 +614,7 @@
         <v>450000000</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9288130</v>
       </c>
@@ -613,7 +629,7 @@
         <v>1107550000</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9288132</v>
       </c>
@@ -627,7 +643,7 @@
         <v>300000000</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9288133</v>
       </c>
@@ -641,7 +657,7 @@
         <v>700000000</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9288134</v>
       </c>
@@ -655,7 +671,7 @@
         <v>98860000</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9288135</v>
       </c>
@@ -669,7 +685,7 @@
         <v>1345000</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9288136</v>
       </c>
@@ -683,7 +699,7 @@
         <v>111480000</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9288137</v>
       </c>
@@ -697,7 +713,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9288138</v>
       </c>
@@ -711,7 +727,7 @@
         <v>39614000</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9288139</v>
       </c>
@@ -725,7 +741,7 @@
         <v>3200000</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9288141</v>
       </c>
@@ -739,7 +755,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9288142</v>
       </c>
@@ -753,7 +769,7 @@
         <v>29712000</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9288143</v>
       </c>
@@ -767,7 +783,7 @@
         <v>728000</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9288144</v>
       </c>
@@ -781,7 +797,7 @@
         <v>49000000</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9288145</v>
       </c>
@@ -795,7 +811,7 @@
         <v>45345000</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9288147</v>
       </c>
@@ -809,7 +825,7 @@
         <v>14817323</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9288148</v>
       </c>
@@ -823,7 +839,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9288149</v>
       </c>
@@ -837,7 +853,7 @@
         <v>5000000</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9288150</v>
       </c>
@@ -851,7 +867,7 @@
         <v>10671300</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9288152</v>
       </c>
@@ -865,7 +881,7 @@
         <v>15130000</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9288153</v>
       </c>
@@ -879,7 +895,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9288154</v>
       </c>
@@ -893,7 +909,7 @@
         <v>650000</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9288155</v>
       </c>
@@ -907,7 +923,7 @@
         <v>5100000</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9288167</v>
       </c>
@@ -921,7 +937,7 @@
         <v>3773400</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9288168</v>
       </c>
@@ -935,7 +951,7 @@
         <v>130000000</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9288169</v>
       </c>
@@ -949,7 +965,7 @@
         <v>43368482</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9288176</v>
       </c>
@@ -964,7 +980,7 @@
         <v>23131467.960000001</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9288177</v>
       </c>
@@ -978,7 +994,7 @@
         <v>100370000</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9288178</v>
       </c>
@@ -992,7 +1008,7 @@
         <v>253000000</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9288179</v>
       </c>
@@ -1006,7 +1022,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9288180</v>
       </c>
@@ -1020,7 +1036,7 @@
         <v>3072030000</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9288181</v>
       </c>
@@ -1034,7 +1050,7 @@
         <v>75352000</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9288182</v>
       </c>
@@ -1048,7 +1064,7 @@
         <v>7000000</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9288183</v>
       </c>
@@ -1062,7 +1078,7 @@
         <v>8000000</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9288185</v>
       </c>
@@ -1076,7 +1092,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>9288186</v>
       </c>
@@ -1090,7 +1106,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>9288187</v>
       </c>
@@ -1104,7 +1120,7 @@
         <v>36000000</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>9288188</v>
       </c>
@@ -1118,7 +1134,7 @@
         <v>8647600</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>9288189</v>
       </c>
@@ -1132,7 +1148,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>9288190</v>
       </c>
@@ -1146,7 +1162,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>9288191</v>
       </c>
@@ -1160,7 +1176,7 @@
         <v>210000000</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>9288192</v>
       </c>
@@ -1174,7 +1190,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>9288193</v>
       </c>
@@ -1188,7 +1204,7 @@
         <v>3900000</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>9288194</v>
       </c>
@@ -1202,7 +1218,7 @@
         <v>3600000</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>9288195</v>
       </c>
@@ -1216,7 +1232,7 @@
         <v>749679</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>9288196</v>
       </c>
@@ -1230,7 +1246,7 @@
         <v>42412000</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>9288198</v>
       </c>
@@ -1244,7 +1260,7 @@
         <v>985935044</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>9288209</v>
       </c>
@@ -1258,7 +1274,7 @@
         <v>1200000</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>9288210</v>
       </c>
@@ -1272,7 +1288,7 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>9288211</v>
       </c>
@@ -1286,7 +1302,7 @@
         <v>3200000</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>9288212</v>
       </c>
@@ -1300,7 +1316,7 @@
         <v>2050000000</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>9288213</v>
       </c>
@@ -1314,7 +1330,7 @@
         <v>23000005</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>9288214</v>
       </c>
@@ -1328,7 +1344,7 @@
         <v>199489167.000002</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>9321270</v>
       </c>
@@ -1342,7 +1358,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>9334530</v>
       </c>
@@ -1356,9 +1372,9 @@
         <v>14000000</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>9999999</v>
+        <v>999999</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>63</v>
@@ -1377,9 +1393,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="6.7109375" bestFit="1" customWidth="1"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6299D06-EE63-429C-BEF3-4B744F9C17CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C9AF39-554D-41B3-90AA-326859EFF397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>999999</v>
+        <v>9999999</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>63</v>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
-  <workbookPr hidePivotFieldList="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Silviana\Documents\1. CGE\tele-trabalho\GIT\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m13368964\Documents\tele-trabalho\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C9AF39-554D-41B3-90AA-326859EFF397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867"/>
   </bookViews>
   <sheets>
     <sheet name="projetos" sheetId="9" r:id="rId1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="64">
   <si>
     <t>II.3</t>
   </si>
@@ -236,7 +235,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -573,8 +572,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D57"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1386,6 +1385,20 @@
         <v>427970000</v>
       </c>
     </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>9334530</v>
+      </c>
+      <c r="B58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="3">
+        <v>14000000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1393,7 +1406,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">projetos!$A$1:$D$56</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
   <si>
     <t>II.3</t>
   </si>
@@ -353,7 +353,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -388,7 +388,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -573,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1383,20 +1383,6 @@
       </c>
       <c r="D57" s="2">
         <v>427970000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>9334530</v>
-      </c>
-      <c r="B58" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="3">
-        <v>14000000</v>
       </c>
     </row>
   </sheetData>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="64">
   <si>
     <t>II.3</t>
   </si>
@@ -276,7 +276,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -292,6 +292,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1382,6 +1386,20 @@
         <v>2</v>
       </c>
       <c r="D57" s="2">
+        <v>427970000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="7">
+        <v>9999999</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" s="2">
         <v>427970000</v>
       </c>
     </row>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
   <si>
     <t>II.3</t>
   </si>
@@ -276,7 +276,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -292,10 +292,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -577,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1386,20 +1382,6 @@
         <v>2</v>
       </c>
       <c r="D57" s="2">
-        <v>427970000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="7">
-        <v>9999999</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D58" s="2">
         <v>427970000</v>
       </c>
     </row>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -1372,9 +1372,6 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>9999999</v>
-      </c>
       <c r="B57" s="6" t="s">
         <v>63</v>
       </c>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -239,7 +239,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,6 +248,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -276,7 +284,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -292,6 +300,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1372,6 +1383,9 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>9999999</v>
+      </c>
       <c r="B57" s="6" t="s">
         <v>63</v>
       </c>
@@ -1381,6 +1395,9 @@
       <c r="D57" s="2">
         <v>427970000</v>
       </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m13368964\Documents\tele-trabalho\transparencia-mg\acordo-judicial-reparacao-vale\upload\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+  <workbookPr hidePivotFieldList="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="867"/>
   </bookViews>
@@ -16,9 +11,9 @@
     <sheet name="Plan1" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">projetos!$A$1:$D$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">projetos!$A$1:$L$60</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="144525"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +25,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -38,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="67">
   <si>
     <t>II.3</t>
   </si>
@@ -230,16 +224,25 @@
   </si>
   <si>
     <t>Complementação dos recursos federais para o Metrô da RMBH</t>
+  </si>
+  <si>
+    <t>Ampliação da capacidade de cobertura da malha aérea da Polícia Militar de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Melhoria da infraestrutura dos municípios - Mobilidade regional na Bacia do Paraopeba</t>
+  </si>
+  <si>
+    <t>Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG / conclusão de corredor logístico estruturante, conforme critérios técnicos da Seinfra - Mobilidade regional na Bacia do Paraopeba</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,21 +257,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -284,7 +285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -300,8 +301,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -364,7 +376,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -399,7 +411,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -576,7 +588,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -584,11 +596,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="29" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="62.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="11" width="9.140625" style="1"/>
@@ -597,7 +609,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>57</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -611,36 +623,36 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="A2" s="8">
         <v>9288130</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3">
-        <v>450000000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>9288130</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3">
         <f>1048250000+59300000</f>
         <v>1107550000</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>9288130</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3">
+        <v>450000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
         <v>9288132</v>
       </c>
       <c r="B4" t="s">
@@ -654,7 +666,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="8">
         <v>9288133</v>
       </c>
       <c r="B5" t="s">
@@ -668,7 +680,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="8">
         <v>9288134</v>
       </c>
       <c r="B6" t="s">
@@ -682,7 +694,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="8">
         <v>9288135</v>
       </c>
       <c r="B7" t="s">
@@ -696,7 +708,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="8">
         <v>9288136</v>
       </c>
       <c r="B8" t="s">
@@ -710,7 +722,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="8">
         <v>9288137</v>
       </c>
       <c r="B9" t="s">
@@ -724,7 +736,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="8">
         <v>9288138</v>
       </c>
       <c r="B10" t="s">
@@ -738,7 +750,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="8">
         <v>9288139</v>
       </c>
       <c r="B11" t="s">
@@ -752,7 +764,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="8">
         <v>9288141</v>
       </c>
       <c r="B12" t="s">
@@ -766,7 +778,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="8">
         <v>9288142</v>
       </c>
       <c r="B13" t="s">
@@ -780,7 +792,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="8">
         <v>9288143</v>
       </c>
       <c r="B14" t="s">
@@ -794,7 +806,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="8">
         <v>9288144</v>
       </c>
       <c r="B15" t="s">
@@ -808,7 +820,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="8">
         <v>9288145</v>
       </c>
       <c r="B16" t="s">
@@ -822,7 +834,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="8">
         <v>9288147</v>
       </c>
       <c r="B17" t="s">
@@ -836,7 +848,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="8">
         <v>9288148</v>
       </c>
       <c r="B18" t="s">
@@ -850,7 +862,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="8">
         <v>9288149</v>
       </c>
       <c r="B19" t="s">
@@ -864,7 +876,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20">
+      <c r="A20" s="8">
         <v>9288150</v>
       </c>
       <c r="B20" t="s">
@@ -878,7 +890,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="8">
         <v>9288152</v>
       </c>
       <c r="B21" t="s">
@@ -892,7 +904,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22">
+      <c r="A22" s="8">
         <v>9288153</v>
       </c>
       <c r="B22" t="s">
@@ -906,7 +918,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="8">
         <v>9288154</v>
       </c>
       <c r="B23" t="s">
@@ -920,7 +932,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24">
+      <c r="A24" s="8">
         <v>9288155</v>
       </c>
       <c r="B24" t="s">
@@ -934,7 +946,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="A25" s="8">
         <v>9288167</v>
       </c>
       <c r="B25" t="s">
@@ -948,7 +960,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26">
+      <c r="A26" s="8">
         <v>9288168</v>
       </c>
       <c r="B26" t="s">
@@ -962,7 +974,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="A27" s="8">
         <v>9288169</v>
       </c>
       <c r="B27" t="s">
@@ -976,7 +988,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="A28" s="8">
         <v>9288176</v>
       </c>
       <c r="B28" t="s">
@@ -991,7 +1003,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="A29" s="8">
         <v>9288177</v>
       </c>
       <c r="B29" t="s">
@@ -1000,12 +1012,12 @@
       <c r="C29" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="3">
-        <v>100370000</v>
+      <c r="D29" s="11">
+        <v>88370000</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="A30" s="8">
         <v>9288178</v>
       </c>
       <c r="B30" t="s">
@@ -1019,7 +1031,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="A31" s="8">
         <v>9288179</v>
       </c>
       <c r="B31" t="s">
@@ -1033,7 +1045,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="A32" s="8">
         <v>9288180</v>
       </c>
       <c r="B32" t="s">
@@ -1047,7 +1059,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="A33" s="8">
         <v>9288181</v>
       </c>
       <c r="B33" t="s">
@@ -1061,7 +1073,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="A34" s="8">
         <v>9288182</v>
       </c>
       <c r="B34" t="s">
@@ -1075,7 +1087,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35">
+      <c r="A35" s="8">
         <v>9288183</v>
       </c>
       <c r="B35" t="s">
@@ -1089,7 +1101,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="A36" s="8">
         <v>9288185</v>
       </c>
       <c r="B36" t="s">
@@ -1103,7 +1115,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37">
+      <c r="A37" s="8">
         <v>9288186</v>
       </c>
       <c r="B37" t="s">
@@ -1117,7 +1129,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="A38" s="8">
         <v>9288187</v>
       </c>
       <c r="B38" t="s">
@@ -1131,7 +1143,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="A39" s="8">
         <v>9288188</v>
       </c>
       <c r="B39" t="s">
@@ -1145,7 +1157,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="A40" s="8">
         <v>9288189</v>
       </c>
       <c r="B40" t="s">
@@ -1159,7 +1171,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41">
+      <c r="A41" s="8">
         <v>9288190</v>
       </c>
       <c r="B41" t="s">
@@ -1173,7 +1185,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42">
+      <c r="A42" s="8">
         <v>9288191</v>
       </c>
       <c r="B42" t="s">
@@ -1187,7 +1199,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="A43" s="8">
         <v>9288192</v>
       </c>
       <c r="B43" t="s">
@@ -1201,7 +1213,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44">
+      <c r="A44" s="8">
         <v>9288193</v>
       </c>
       <c r="B44" t="s">
@@ -1215,7 +1227,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="A45" s="8">
         <v>9288194</v>
       </c>
       <c r="B45" t="s">
@@ -1229,7 +1241,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46">
+      <c r="A46" s="8">
         <v>9288195</v>
       </c>
       <c r="B46" t="s">
@@ -1243,7 +1255,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47">
+      <c r="A47" s="8">
         <v>9288196</v>
       </c>
       <c r="B47" t="s">
@@ -1257,7 +1269,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48">
+      <c r="A48" s="8">
         <v>9288198</v>
       </c>
       <c r="B48" t="s">
@@ -1271,7 +1283,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49">
+      <c r="A49" s="8">
         <v>9288209</v>
       </c>
       <c r="B49" t="s">
@@ -1285,7 +1297,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50">
+      <c r="A50" s="8">
         <v>9288210</v>
       </c>
       <c r="B50" t="s">
@@ -1299,7 +1311,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51">
+      <c r="A51" s="8">
         <v>9288211</v>
       </c>
       <c r="B51" t="s">
@@ -1313,7 +1325,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52">
+      <c r="A52" s="8">
         <v>9288212</v>
       </c>
       <c r="B52" t="s">
@@ -1327,7 +1339,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53">
+      <c r="A53" s="8">
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
@@ -1341,7 +1353,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54">
+      <c r="A54" s="8">
         <v>9288214</v>
       </c>
       <c r="B54" t="s">
@@ -1355,7 +1367,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55">
+      <c r="A55" s="8">
         <v>9321270</v>
       </c>
       <c r="B55" t="s">
@@ -1369,7 +1381,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56">
+      <c r="A56" s="8">
         <v>9334530</v>
       </c>
       <c r="B56" t="s">
@@ -1383,8 +1395,8 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
-        <v>9999999</v>
+      <c r="A57" s="12">
+        <v>9337957</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>63</v>
@@ -1397,9 +1409,51 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="7"/>
+      <c r="A58" s="8">
+        <v>9341846</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="3">
+        <v>12000000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="8">
+        <v>9999999</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="3">
+        <v>56352383.469999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="8">
+        <v>9999999</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" s="3">
+        <v>47997269.119999997</v>
+      </c>
     </row>
   </sheetData>
+  <sortState ref="A2:D61">
+    <sortCondition ref="A1:A61"/>
+  </sortState>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
   <si>
     <t>II.3</t>
   </si>
@@ -229,10 +229,10 @@
     <t>Ampliação da capacidade de cobertura da malha aérea da Polícia Militar de Minas Gerais</t>
   </si>
   <si>
-    <t>Melhoria da infraestrutura dos municípios - Mobilidade regional na Bacia do Paraopeba</t>
-  </si>
-  <si>
-    <t>Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG / conclusão de corredor logístico estruturante, conforme critérios técnicos da Seinfra - Mobilidade regional na Bacia do Paraopeba</t>
+    <t>Mobilidade regional na Bacia do Paraopeba</t>
+  </si>
+  <si>
+    <t>III e IV</t>
   </si>
 </sst>
 </file>
@@ -285,7 +285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -300,7 +300,6 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -310,11 +309,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,7 +583,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -596,10 +591,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" style="8" customWidth="1"/>
     <col min="2" max="2" width="62.7109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
     <col min="4" max="4" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -609,7 +604,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -623,7 +618,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>9288130</v>
       </c>
       <c r="B2" t="s">
@@ -638,7 +633,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="A3" s="7">
         <v>9288130</v>
       </c>
       <c r="B3" t="s">
@@ -652,7 +647,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="A4" s="7">
         <v>9288132</v>
       </c>
       <c r="B4" t="s">
@@ -666,7 +661,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="A5" s="7">
         <v>9288133</v>
       </c>
       <c r="B5" t="s">
@@ -680,7 +675,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="A6" s="7">
         <v>9288134</v>
       </c>
       <c r="B6" t="s">
@@ -694,7 +689,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="A7" s="7">
         <v>9288135</v>
       </c>
       <c r="B7" t="s">
@@ -708,7 +703,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="A8" s="7">
         <v>9288136</v>
       </c>
       <c r="B8" t="s">
@@ -722,7 +717,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="A9" s="7">
         <v>9288137</v>
       </c>
       <c r="B9" t="s">
@@ -736,7 +731,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+      <c r="A10" s="7">
         <v>9288138</v>
       </c>
       <c r="B10" t="s">
@@ -750,7 +745,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="A11" s="7">
         <v>9288139</v>
       </c>
       <c r="B11" t="s">
@@ -764,7 +759,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
+      <c r="A12" s="7">
         <v>9288141</v>
       </c>
       <c r="B12" t="s">
@@ -778,7 +773,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="A13" s="7">
         <v>9288142</v>
       </c>
       <c r="B13" t="s">
@@ -792,7 +787,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
+      <c r="A14" s="7">
         <v>9288143</v>
       </c>
       <c r="B14" t="s">
@@ -806,7 +801,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+      <c r="A15" s="7">
         <v>9288144</v>
       </c>
       <c r="B15" t="s">
@@ -820,7 +815,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
+      <c r="A16" s="7">
         <v>9288145</v>
       </c>
       <c r="B16" t="s">
@@ -834,7 +829,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+      <c r="A17" s="7">
         <v>9288147</v>
       </c>
       <c r="B17" t="s">
@@ -848,7 +843,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
+      <c r="A18" s="7">
         <v>9288148</v>
       </c>
       <c r="B18" t="s">
@@ -862,7 +857,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="8">
+      <c r="A19" s="7">
         <v>9288149</v>
       </c>
       <c r="B19" t="s">
@@ -876,7 +871,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="8">
+      <c r="A20" s="7">
         <v>9288150</v>
       </c>
       <c r="B20" t="s">
@@ -890,7 +885,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="8">
+      <c r="A21" s="7">
         <v>9288152</v>
       </c>
       <c r="B21" t="s">
@@ -904,7 +899,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="8">
+      <c r="A22" s="7">
         <v>9288153</v>
       </c>
       <c r="B22" t="s">
@@ -918,7 +913,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="8">
+      <c r="A23" s="7">
         <v>9288154</v>
       </c>
       <c r="B23" t="s">
@@ -932,7 +927,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="8">
+      <c r="A24" s="7">
         <v>9288155</v>
       </c>
       <c r="B24" t="s">
@@ -946,7 +941,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="8">
+      <c r="A25" s="7">
         <v>9288167</v>
       </c>
       <c r="B25" t="s">
@@ -960,7 +955,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="8">
+      <c r="A26" s="7">
         <v>9288168</v>
       </c>
       <c r="B26" t="s">
@@ -974,7 +969,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="8">
+      <c r="A27" s="7">
         <v>9288169</v>
       </c>
       <c r="B27" t="s">
@@ -988,7 +983,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="8">
+      <c r="A28" s="7">
         <v>9288176</v>
       </c>
       <c r="B28" t="s">
@@ -1003,7 +998,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="8">
+      <c r="A29" s="7">
         <v>9288177</v>
       </c>
       <c r="B29" t="s">
@@ -1012,12 +1007,12 @@
       <c r="C29" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="9">
         <v>88370000</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="8">
+      <c r="A30" s="7">
         <v>9288178</v>
       </c>
       <c r="B30" t="s">
@@ -1031,7 +1026,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="8">
+      <c r="A31" s="7">
         <v>9288179</v>
       </c>
       <c r="B31" t="s">
@@ -1045,7 +1040,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="8">
+      <c r="A32" s="7">
         <v>9288180</v>
       </c>
       <c r="B32" t="s">
@@ -1059,7 +1054,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="8">
+      <c r="A33" s="7">
         <v>9288181</v>
       </c>
       <c r="B33" t="s">
@@ -1073,7 +1068,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="8">
+      <c r="A34" s="7">
         <v>9288182</v>
       </c>
       <c r="B34" t="s">
@@ -1087,7 +1082,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="8">
+      <c r="A35" s="7">
         <v>9288183</v>
       </c>
       <c r="B35" t="s">
@@ -1101,7 +1096,7 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="8">
+      <c r="A36" s="7">
         <v>9288185</v>
       </c>
       <c r="B36" t="s">
@@ -1115,7 +1110,7 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="8">
+      <c r="A37" s="7">
         <v>9288186</v>
       </c>
       <c r="B37" t="s">
@@ -1129,7 +1124,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="8">
+      <c r="A38" s="7">
         <v>9288187</v>
       </c>
       <c r="B38" t="s">
@@ -1143,7 +1138,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="8">
+      <c r="A39" s="7">
         <v>9288188</v>
       </c>
       <c r="B39" t="s">
@@ -1157,7 +1152,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="8">
+      <c r="A40" s="7">
         <v>9288189</v>
       </c>
       <c r="B40" t="s">
@@ -1171,7 +1166,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="8">
+      <c r="A41" s="7">
         <v>9288190</v>
       </c>
       <c r="B41" t="s">
@@ -1185,7 +1180,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="8">
+      <c r="A42" s="7">
         <v>9288191</v>
       </c>
       <c r="B42" t="s">
@@ -1199,7 +1194,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="8">
+      <c r="A43" s="7">
         <v>9288192</v>
       </c>
       <c r="B43" t="s">
@@ -1213,7 +1208,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="8">
+      <c r="A44" s="7">
         <v>9288193</v>
       </c>
       <c r="B44" t="s">
@@ -1227,7 +1222,7 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="8">
+      <c r="A45" s="7">
         <v>9288194</v>
       </c>
       <c r="B45" t="s">
@@ -1241,7 +1236,7 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="8">
+      <c r="A46" s="7">
         <v>9288195</v>
       </c>
       <c r="B46" t="s">
@@ -1255,7 +1250,7 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="8">
+      <c r="A47" s="7">
         <v>9288196</v>
       </c>
       <c r="B47" t="s">
@@ -1269,7 +1264,7 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="8">
+      <c r="A48" s="7">
         <v>9288198</v>
       </c>
       <c r="B48" t="s">
@@ -1283,7 +1278,7 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="8">
+      <c r="A49" s="7">
         <v>9288209</v>
       </c>
       <c r="B49" t="s">
@@ -1297,7 +1292,7 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="8">
+      <c r="A50" s="7">
         <v>9288210</v>
       </c>
       <c r="B50" t="s">
@@ -1311,7 +1306,7 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="8">
+      <c r="A51" s="7">
         <v>9288211</v>
       </c>
       <c r="B51" t="s">
@@ -1325,7 +1320,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="8">
+      <c r="A52" s="7">
         <v>9288212</v>
       </c>
       <c r="B52" t="s">
@@ -1339,7 +1334,7 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="8">
+      <c r="A53" s="7">
         <v>9288213</v>
       </c>
       <c r="B53" t="s">
@@ -1353,7 +1348,7 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="8">
+      <c r="A54" s="7">
         <v>9288214</v>
       </c>
       <c r="B54" t="s">
@@ -1367,7 +1362,7 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="8">
+      <c r="A55" s="7">
         <v>9321270</v>
       </c>
       <c r="B55" t="s">
@@ -1381,7 +1376,7 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="8">
+      <c r="A56" s="7">
         <v>9334530</v>
       </c>
       <c r="B56" t="s">
@@ -1395,24 +1390,24 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="12">
+      <c r="A57" s="7">
         <v>9337957</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" t="s">
         <v>63</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="2">
+      <c r="D57" s="3">
         <v>427970000</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="8">
+      <c r="A58" s="7">
         <v>9341846</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" t="s">
         <v>64</v>
       </c>
       <c r="C58" t="s">
@@ -1423,32 +1418,36 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="8">
-        <v>9999999</v>
-      </c>
-      <c r="B59" s="10" t="s">
+      <c r="A59" s="7">
+        <v>9342884</v>
+      </c>
+      <c r="B59" t="s">
         <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="D59" s="3">
-        <v>56352383.469999999</v>
+        <v>104349652.59</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="8">
-        <v>9999999</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C60" t="s">
-        <v>2</v>
-      </c>
-      <c r="D60" s="3">
-        <v>47997269.119999997</v>
-      </c>
+      <c r="A60" s="7"/>
+      <c r="B60"/>
+      <c r="C60"/>
+      <c r="D60" s="3"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="7"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61" s="3"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="7"/>
+      <c r="B62"/>
+      <c r="C62"/>
+      <c r="D62" s="3"/>
     </row>
   </sheetData>
   <sortState ref="A2:D61">

--- a/upload/projetos_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/projetos_acordo_judicial_reparacao_vale.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="67">
   <si>
     <t>II.3</t>
   </si>
@@ -229,10 +229,10 @@
     <t>Ampliação da capacidade de cobertura da malha aérea da Polícia Militar de Minas Gerais</t>
   </si>
   <si>
-    <t>Mobilidade regional na Bacia do Paraopeba</t>
-  </si>
-  <si>
-    <t>III e IV</t>
+    <t>Melhoria da infraestrutura dos municípios - Mobilidade regional na Bacia do Paraopeba</t>
+  </si>
+  <si>
+    <t>Recuperação de rodovias pavimentadas em pior estado, conforme avaliação técnica do DER-MG / conclusão de corredor logístico estruturante, conforme critérios técnicos da Seinfra - Mobilidade regional na Bacia do Paraopeba</t>
   </si>
 </sst>
 </file>
@@ -591,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" style="8" customWidth="1"/>
@@ -1425,29 +1425,31 @@
         <v>65</v>
       </c>
       <c r="C59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="3">
+        <v>56352383.469999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="7">
+        <v>9342884</v>
+      </c>
+      <c r="B60" t="s">
         <v>66</v>
       </c>
-      <c r="D59" s="3">
-        <v>104349652.59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="7"/>
-      <c r="B60"/>
-      <c r="C60"/>
-      <c r="D60" s="3"/>
+      <c r="C60" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" s="3">
+        <v>47997269.119999997</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="7"/>
       <c r="B61"/>
       <c r="C61"/>
       <c r="D61" s="3"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="7"/>
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62" s="3"/>
     </row>
   </sheetData>
   <sortState ref="A2:D61">
